--- a/output/yearly_population_iteration_94_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_94_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6318</v>
+        <v>5703</v>
       </c>
       <c r="C2" t="n">
-        <v>10307</v>
+        <v>4281</v>
       </c>
       <c r="D2" t="n">
-        <v>30453</v>
+        <v>24445</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3340</v>
+        <v>3961</v>
       </c>
       <c r="C3" t="n">
-        <v>5461</v>
+        <v>2234</v>
       </c>
       <c r="D3" t="n">
-        <v>16113</v>
+        <v>12116</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2797</v>
+        <v>2794</v>
       </c>
       <c r="C4" t="n">
-        <v>5291</v>
+        <v>2525</v>
       </c>
       <c r="D4" t="n">
-        <v>7544</v>
+        <v>5627</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1795</v>
+        <v>1874</v>
       </c>
       <c r="C5" t="n">
-        <v>5619</v>
+        <v>2610</v>
       </c>
       <c r="D5" t="n">
-        <v>2918</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1022</v>
+        <v>1111</v>
       </c>
       <c r="C6" t="n">
-        <v>3992</v>
+        <v>2367</v>
       </c>
       <c r="D6" t="n">
-        <v>1231</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>475</v>
+        <v>513</v>
       </c>
       <c r="C7" t="n">
-        <v>2131</v>
+        <v>1506</v>
       </c>
       <c r="D7" t="n">
-        <v>657</v>
+        <v>668</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>169</v>
+        <v>185</v>
       </c>
       <c r="C8" t="n">
-        <v>884</v>
+        <v>711</v>
       </c>
       <c r="D8" t="n">
-        <v>432</v>
+        <v>437</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C9" t="n">
-        <v>369</v>
+        <v>323</v>
       </c>
       <c r="D9" t="n">
-        <v>306</v>
+        <v>310</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C10" t="n">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D10" t="n">
-        <v>246</v>
+        <v>251</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C11" t="n">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="D11" t="n">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="D12" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="13">
@@ -937,7 +937,7 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="D13" t="n">
         <v>124</v>
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15">
@@ -965,7 +965,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="D15" t="n">
         <v>82</v>
@@ -979,10 +979,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -993,7 +993,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -1010,7 +1010,7 @@
         <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19">
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1049,10 +1049,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6696</v>
+        <v>7086</v>
       </c>
       <c r="C2" t="n">
-        <v>12944</v>
+        <v>8195</v>
       </c>
       <c r="D2" t="n">
-        <v>26871</v>
+        <v>26686</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3729</v>
+        <v>3909</v>
       </c>
       <c r="C3" t="n">
-        <v>6684</v>
+        <v>2835</v>
       </c>
       <c r="D3" t="n">
-        <v>16891</v>
+        <v>13057</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2591</v>
+        <v>2875</v>
       </c>
       <c r="C4" t="n">
-        <v>5208</v>
+        <v>2321</v>
       </c>
       <c r="D4" t="n">
-        <v>8558</v>
+        <v>6523</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1974</v>
+        <v>2027</v>
       </c>
       <c r="C5" t="n">
-        <v>5354</v>
+        <v>2513</v>
       </c>
       <c r="D5" t="n">
-        <v>3539</v>
+        <v>2876</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1218</v>
+        <v>1343</v>
       </c>
       <c r="C6" t="n">
-        <v>4618</v>
+        <v>2435</v>
       </c>
       <c r="D6" t="n">
-        <v>1445</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="7">
@@ -1161,10 +1161,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>625</v>
+        <v>699</v>
       </c>
       <c r="C7" t="n">
-        <v>2932</v>
+        <v>1918</v>
       </c>
       <c r="D7" t="n">
         <v>734</v>
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>256</v>
+        <v>290</v>
       </c>
       <c r="C8" t="n">
-        <v>1388</v>
+        <v>1069</v>
       </c>
       <c r="D8" t="n">
-        <v>454</v>
+        <v>468</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="C9" t="n">
-        <v>575</v>
+        <v>497</v>
       </c>
       <c r="D9" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C10" t="n">
-        <v>269</v>
+        <v>259</v>
       </c>
       <c r="D10" t="n">
-        <v>248</v>
+        <v>257</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C11" t="n">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="D11" t="n">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="D12" t="n">
-        <v>163</v>
+        <v>166</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="D13" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -1304,7 +1304,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -1321,7 +1321,7 @@
         <v>35</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19">
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1360,10 +1360,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7418</v>
+        <v>8298</v>
       </c>
       <c r="C2" t="n">
-        <v>20683</v>
+        <v>8093</v>
       </c>
       <c r="D2" t="n">
-        <v>22213</v>
+        <v>37226</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3961</v>
+        <v>4289</v>
       </c>
       <c r="C3" t="n">
-        <v>8149</v>
+        <v>4638</v>
       </c>
       <c r="D3" t="n">
-        <v>17007</v>
+        <v>14033</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2578</v>
+        <v>2835</v>
       </c>
       <c r="C4" t="n">
-        <v>5723</v>
+        <v>2519</v>
       </c>
       <c r="D4" t="n">
-        <v>9497</v>
+        <v>7391</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1976</v>
+        <v>2122</v>
       </c>
       <c r="C5" t="n">
-        <v>5132</v>
+        <v>2348</v>
       </c>
       <c r="D5" t="n">
-        <v>4071</v>
+        <v>3321</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1374</v>
+        <v>1512</v>
       </c>
       <c r="C6" t="n">
-        <v>4822</v>
+        <v>2446</v>
       </c>
       <c r="D6" t="n">
-        <v>1707</v>
+        <v>1517</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>764</v>
+        <v>872</v>
       </c>
       <c r="C7" t="n">
-        <v>3591</v>
+        <v>2126</v>
       </c>
       <c r="D7" t="n">
-        <v>809</v>
+        <v>801</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>350</v>
+        <v>406</v>
       </c>
       <c r="C8" t="n">
-        <v>1948</v>
+        <v>1434</v>
       </c>
       <c r="D8" t="n">
-        <v>480</v>
+        <v>502</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>131</v>
+        <v>157</v>
       </c>
       <c r="C9" t="n">
-        <v>863</v>
+        <v>727</v>
       </c>
       <c r="D9" t="n">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="C10" t="n">
-        <v>376</v>
+        <v>354</v>
       </c>
       <c r="D10" t="n">
-        <v>251</v>
+        <v>263</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C11" t="n">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="D11" t="n">
-        <v>207</v>
+        <v>204</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C12" t="n">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="D12" t="n">
-        <v>164</v>
+        <v>168</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C13" t="n">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="D13" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -1615,7 +1615,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -1629,10 +1629,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19">
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1671,10 +1671,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6853</v>
+        <v>7454</v>
       </c>
       <c r="C2" t="n">
-        <v>14395</v>
+        <v>5244</v>
       </c>
       <c r="D2" t="n">
-        <v>18586</v>
+        <v>29589</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4660</v>
+        <v>5265</v>
       </c>
       <c r="C3" t="n">
-        <v>12446</v>
+        <v>6601</v>
       </c>
       <c r="D3" t="n">
-        <v>18427</v>
+        <v>15791</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1825</v>
+        <v>1960</v>
       </c>
       <c r="C4" t="n">
-        <v>7948</v>
+        <v>3753</v>
       </c>
       <c r="D4" t="n">
-        <v>9013</v>
+        <v>7198</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1269</v>
+        <v>1397</v>
       </c>
       <c r="C5" t="n">
-        <v>4725</v>
+        <v>2397</v>
       </c>
       <c r="D5" t="n">
-        <v>2767</v>
+        <v>2443</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>705</v>
+        <v>805</v>
       </c>
       <c r="C6" t="n">
-        <v>3519</v>
+        <v>2083</v>
       </c>
       <c r="D6" t="n">
-        <v>792</v>
+        <v>784</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>323</v>
+        <v>375</v>
       </c>
       <c r="C7" t="n">
-        <v>1909</v>
+        <v>1405</v>
       </c>
       <c r="D7" t="n">
-        <v>470</v>
+        <v>491</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>121</v>
+        <v>145</v>
       </c>
       <c r="C8" t="n">
-        <v>845</v>
+        <v>712</v>
       </c>
       <c r="D8" t="n">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="C9" t="n">
-        <v>368</v>
+        <v>346</v>
       </c>
       <c r="D9" t="n">
-        <v>245</v>
+        <v>257</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C10" t="n">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D10" t="n">
-        <v>202</v>
+        <v>199</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C11" t="n">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="D11" t="n">
-        <v>160</v>
+        <v>164</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C12" t="n">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D12" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="D13" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D15" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="16">
@@ -1912,7 +1912,7 @@
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D16" t="n">
         <v>50</v>
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D17" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="18">
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D19" t="n">
         <v>15</v>
@@ -1968,10 +1968,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4178</v>
+        <v>4602</v>
       </c>
       <c r="C2" t="n">
-        <v>6886</v>
+        <v>2539</v>
       </c>
       <c r="D2" t="n">
-        <v>13394</v>
+        <v>21667</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4798</v>
+        <v>5390</v>
       </c>
       <c r="C3" t="n">
-        <v>12090</v>
+        <v>5349</v>
       </c>
       <c r="D3" t="n">
-        <v>17564</v>
+        <v>16843</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2491</v>
+        <v>2862</v>
       </c>
       <c r="C4" t="n">
-        <v>10117</v>
+        <v>5240</v>
       </c>
       <c r="D4" t="n">
-        <v>10267</v>
+        <v>8519</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1405</v>
+        <v>1551</v>
       </c>
       <c r="C5" t="n">
-        <v>6122</v>
+        <v>3061</v>
       </c>
       <c r="D5" t="n">
-        <v>3455</v>
+        <v>3054</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>827</v>
+        <v>974</v>
       </c>
       <c r="C6" t="n">
-        <v>4094</v>
+        <v>2305</v>
       </c>
       <c r="D6" t="n">
-        <v>976</v>
+        <v>972</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>301</v>
+        <v>364</v>
       </c>
       <c r="C7" t="n">
-        <v>2486</v>
+        <v>1734</v>
       </c>
       <c r="D7" t="n">
-        <v>512</v>
+        <v>534</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>101</v>
+        <v>122</v>
       </c>
       <c r="C8" t="n">
-        <v>1124</v>
+        <v>948</v>
       </c>
       <c r="D8" t="n">
-        <v>335</v>
+        <v>349</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="C9" t="n">
-        <v>402</v>
+        <v>416</v>
       </c>
       <c r="D9" t="n">
-        <v>256</v>
+        <v>265</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C10" t="n">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="D10" t="n">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C11" t="n">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="D11" t="n">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="D12" t="n">
-        <v>130</v>
+        <v>133</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D14" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15">
@@ -2209,7 +2209,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D15" t="n">
         <v>49</v>
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D16" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="17">
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D18" t="n">
         <v>14</v>
@@ -2265,10 +2265,10 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4160</v>
+        <v>4689</v>
       </c>
       <c r="C2" t="n">
-        <v>15400</v>
+        <v>8621</v>
       </c>
       <c r="D2" t="n">
-        <v>12028</v>
+        <v>20406</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3823</v>
+        <v>4219</v>
       </c>
       <c r="C3" t="n">
-        <v>8673</v>
+        <v>3448</v>
       </c>
       <c r="D3" t="n">
-        <v>15816</v>
+        <v>16552</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2972</v>
+        <v>3480</v>
       </c>
       <c r="C4" t="n">
-        <v>10834</v>
+        <v>5188</v>
       </c>
       <c r="D4" t="n">
-        <v>11145</v>
+        <v>9616</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1642</v>
+        <v>1898</v>
       </c>
       <c r="C5" t="n">
-        <v>7797</v>
+        <v>4135</v>
       </c>
       <c r="D5" t="n">
-        <v>4396</v>
+        <v>3905</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>968</v>
+        <v>1143</v>
       </c>
       <c r="C6" t="n">
-        <v>4971</v>
+        <v>2666</v>
       </c>
       <c r="D6" t="n">
-        <v>1320</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>439</v>
+        <v>543</v>
       </c>
       <c r="C7" t="n">
-        <v>3146</v>
+        <v>1996</v>
       </c>
       <c r="D7" t="n">
-        <v>570</v>
+        <v>602</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>146</v>
+        <v>189</v>
       </c>
       <c r="C8" t="n">
-        <v>1668</v>
+        <v>1303</v>
       </c>
       <c r="D8" t="n">
-        <v>357</v>
+        <v>370</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="C9" t="n">
-        <v>671</v>
+        <v>642</v>
       </c>
       <c r="D9" t="n">
-        <v>261</v>
+        <v>272</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="C10" t="n">
-        <v>281</v>
+        <v>301</v>
       </c>
       <c r="D10" t="n">
-        <v>212</v>
+        <v>216</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C11" t="n">
-        <v>183</v>
+        <v>195</v>
       </c>
       <c r="D11" t="n">
-        <v>168</v>
+        <v>172</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>113</v>
+        <v>127</v>
       </c>
       <c r="D12" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="D14" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="15">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17">
@@ -2562,7 +2562,7 @@
         <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D18" t="n">
         <v>13</v>
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2519</v>
+        <v>2718</v>
       </c>
       <c r="C2" t="n">
-        <v>7441</v>
+        <v>3767</v>
       </c>
       <c r="D2" t="n">
-        <v>8409</v>
+        <v>13943</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3764</v>
+        <v>4183</v>
       </c>
       <c r="C3" t="n">
-        <v>10589</v>
+        <v>5224</v>
       </c>
       <c r="D3" t="n">
-        <v>15067</v>
+        <v>16590</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3256</v>
+        <v>3874</v>
       </c>
       <c r="C4" t="n">
-        <v>10984</v>
+        <v>4943</v>
       </c>
       <c r="D4" t="n">
-        <v>11829</v>
+        <v>10517</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1702</v>
+        <v>2015</v>
       </c>
       <c r="C5" t="n">
-        <v>9730</v>
+        <v>4959</v>
       </c>
       <c r="D5" t="n">
-        <v>4611</v>
+        <v>4337</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>781</v>
+        <v>998</v>
       </c>
       <c r="C6" t="n">
-        <v>5754</v>
+        <v>3484</v>
       </c>
       <c r="D6" t="n">
-        <v>1278</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>134</v>
+        <v>174</v>
       </c>
       <c r="C7" t="n">
-        <v>3195</v>
+        <v>2218</v>
       </c>
       <c r="D7" t="n">
-        <v>572</v>
+        <v>610</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="C8" t="n">
-        <v>1131</v>
+        <v>1076</v>
       </c>
       <c r="D8" t="n">
-        <v>374</v>
+        <v>390</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C9" t="n">
-        <v>275</v>
+        <v>294</v>
       </c>
       <c r="D9" t="n">
-        <v>284</v>
+        <v>294</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C10" t="n">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="D10" t="n">
-        <v>164</v>
+        <v>168</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>110</v>
+        <v>124</v>
       </c>
       <c r="D11" t="n">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14">
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D15" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="16">
@@ -2859,7 +2859,7 @@
         <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
         <v>12</v>
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2740</v>
+        <v>4305</v>
       </c>
       <c r="C2" t="n">
-        <v>11224</v>
+        <v>7355</v>
       </c>
       <c r="D2" t="n">
-        <v>7113</v>
+        <v>13041</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2806</v>
+        <v>3023</v>
       </c>
       <c r="C3" t="n">
-        <v>8245</v>
+        <v>3984</v>
       </c>
       <c r="D3" t="n">
-        <v>13226</v>
+        <v>15067</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3017</v>
+        <v>3510</v>
       </c>
       <c r="C4" t="n">
-        <v>10682</v>
+        <v>5030</v>
       </c>
       <c r="D4" t="n">
-        <v>11966</v>
+        <v>11246</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2044</v>
+        <v>2497</v>
       </c>
       <c r="C5" t="n">
-        <v>10150</v>
+        <v>4895</v>
       </c>
       <c r="D5" t="n">
-        <v>5554</v>
+        <v>5255</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1013</v>
+        <v>1297</v>
       </c>
       <c r="C6" t="n">
-        <v>7325</v>
+        <v>4149</v>
       </c>
       <c r="D6" t="n">
-        <v>1677</v>
+        <v>1703</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>279</v>
+        <v>398</v>
       </c>
       <c r="C7" t="n">
-        <v>4178</v>
+        <v>2806</v>
       </c>
       <c r="D7" t="n">
-        <v>654</v>
+        <v>701</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>62</v>
+        <v>81</v>
       </c>
       <c r="C8" t="n">
-        <v>1860</v>
+        <v>1544</v>
       </c>
       <c r="D8" t="n">
-        <v>389</v>
+        <v>415</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="C9" t="n">
-        <v>543</v>
+        <v>578</v>
       </c>
       <c r="D9" t="n">
-        <v>294</v>
+        <v>303</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>229</v>
       </c>
       <c r="D10" t="n">
-        <v>170</v>
+        <v>177</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>128</v>
+        <v>146</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>103</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D14" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D15" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16">
@@ -3156,7 +3156,7 @@
         <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D16" t="n">
         <v>20</v>
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D18" t="n">
         <v>2</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1973</v>
+        <v>3078</v>
       </c>
       <c r="C2" t="n">
-        <v>6047</v>
+        <v>4730</v>
       </c>
       <c r="D2" t="n">
-        <v>6347</v>
+        <v>9327</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2444</v>
+        <v>3043</v>
       </c>
       <c r="C3" t="n">
-        <v>8599</v>
+        <v>4948</v>
       </c>
       <c r="D3" t="n">
-        <v>11843</v>
+        <v>13963</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2725</v>
+        <v>3088</v>
       </c>
       <c r="C4" t="n">
-        <v>9752</v>
+        <v>4560</v>
       </c>
       <c r="D4" t="n">
-        <v>11874</v>
+        <v>11562</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2213</v>
+        <v>2715</v>
       </c>
       <c r="C5" t="n">
-        <v>10507</v>
+        <v>5035</v>
       </c>
       <c r="D5" t="n">
-        <v>6168</v>
+        <v>5943</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1150</v>
+        <v>1538</v>
       </c>
       <c r="C6" t="n">
-        <v>8424</v>
+        <v>4578</v>
       </c>
       <c r="D6" t="n">
-        <v>1987</v>
+        <v>2056</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>248</v>
+        <v>415</v>
       </c>
       <c r="C7" t="n">
-        <v>5141</v>
+        <v>3379</v>
       </c>
       <c r="D7" t="n">
-        <v>738</v>
+        <v>798</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>49</v>
+        <v>68</v>
       </c>
       <c r="C8" t="n">
-        <v>2355</v>
+        <v>1947</v>
       </c>
       <c r="D8" t="n">
-        <v>394</v>
+        <v>436</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C9" t="n">
-        <v>580</v>
+        <v>724</v>
       </c>
       <c r="D9" t="n">
-        <v>290</v>
+        <v>302</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>215</v>
+        <v>240</v>
       </c>
       <c r="D10" t="n">
-        <v>174</v>
+        <v>181</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>124</v>
+        <v>146</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>140</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="D12" t="n">
-        <v>91</v>
+        <v>96</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15">
@@ -3453,7 +3453,7 @@
         <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D15" t="n">
         <v>19</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2426</v>
+        <v>4835</v>
       </c>
       <c r="C2" t="n">
-        <v>6529</v>
+        <v>3819</v>
       </c>
       <c r="D2" t="n">
-        <v>7010</v>
+        <v>13622</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1931</v>
+        <v>2566</v>
       </c>
       <c r="C3" t="n">
-        <v>6853</v>
+        <v>4324</v>
       </c>
       <c r="D3" t="n">
-        <v>10488</v>
+        <v>12453</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2289</v>
+        <v>2668</v>
       </c>
       <c r="C4" t="n">
-        <v>9095</v>
+        <v>4643</v>
       </c>
       <c r="D4" t="n">
-        <v>11508</v>
+        <v>11579</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2191</v>
+        <v>2629</v>
       </c>
       <c r="C5" t="n">
-        <v>10005</v>
+        <v>4720</v>
       </c>
       <c r="D5" t="n">
-        <v>6692</v>
+        <v>6514</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1358</v>
+        <v>1833</v>
       </c>
       <c r="C6" t="n">
-        <v>9098</v>
+        <v>4728</v>
       </c>
       <c r="D6" t="n">
-        <v>2443</v>
+        <v>2588</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>452</v>
+        <v>716</v>
       </c>
       <c r="C7" t="n">
-        <v>6265</v>
+        <v>3904</v>
       </c>
       <c r="D7" t="n">
-        <v>857</v>
+        <v>962</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>89</v>
+        <v>155</v>
       </c>
       <c r="C8" t="n">
-        <v>3278</v>
+        <v>2493</v>
       </c>
       <c r="D8" t="n">
-        <v>427</v>
+        <v>477</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="C9" t="n">
-        <v>1101</v>
+        <v>1174</v>
       </c>
       <c r="D9" t="n">
-        <v>300</v>
+        <v>317</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C10" t="n">
-        <v>317</v>
+        <v>405</v>
       </c>
       <c r="D10" t="n">
-        <v>181</v>
+        <v>191</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>148</v>
+        <v>175</v>
       </c>
       <c r="D11" t="n">
-        <v>137</v>
+        <v>143</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="D12" t="n">
-        <v>92</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>67</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="15">
@@ -3764,10 +3764,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -3792,7 +3792,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4917</v>
+        <v>4479</v>
       </c>
       <c r="C2" t="n">
-        <v>6951</v>
+        <v>3991</v>
       </c>
       <c r="D2" t="n">
-        <v>8290</v>
+        <v>9864</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1793</v>
+        <v>3347</v>
       </c>
       <c r="C2" t="n">
-        <v>3917</v>
+        <v>2046</v>
       </c>
       <c r="D2" t="n">
-        <v>5271</v>
+        <v>9917</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2580</v>
+        <v>3500</v>
       </c>
       <c r="C3" t="n">
-        <v>7598</v>
+        <v>4536</v>
       </c>
       <c r="D3" t="n">
-        <v>11288</v>
+        <v>13602</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3194</v>
+        <v>3783</v>
       </c>
       <c r="C4" t="n">
-        <v>12474</v>
+        <v>6393</v>
       </c>
       <c r="D4" t="n">
-        <v>11834</v>
+        <v>11887</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1254</v>
+        <v>1839</v>
       </c>
       <c r="C5" t="n">
-        <v>13547</v>
+        <v>6738</v>
       </c>
       <c r="D5" t="n">
-        <v>5975</v>
+        <v>6057</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>417</v>
+        <v>661</v>
       </c>
       <c r="C6" t="n">
-        <v>7655</v>
+        <v>4937</v>
       </c>
       <c r="D6" t="n">
-        <v>1912</v>
+        <v>2104</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>82</v>
+        <v>143</v>
       </c>
       <c r="C7" t="n">
-        <v>3212</v>
+        <v>2443</v>
       </c>
       <c r="D7" t="n">
-        <v>519</v>
+        <v>599</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="C8" t="n">
-        <v>1078</v>
+        <v>1150</v>
       </c>
       <c r="D8" t="n">
-        <v>294</v>
+        <v>310</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C9" t="n">
-        <v>310</v>
+        <v>396</v>
       </c>
       <c r="D9" t="n">
-        <v>177</v>
+        <v>187</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>145</v>
+        <v>171</v>
       </c>
       <c r="D10" t="n">
-        <v>134</v>
+        <v>140</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>83</v>
+        <v>102</v>
       </c>
       <c r="D11" t="n">
-        <v>90</v>
+        <v>96</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D12" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D13" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="14">
@@ -4372,10 +4372,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="D14" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7528</v>
+        <v>7240</v>
       </c>
       <c r="C2" t="n">
-        <v>7194</v>
+        <v>5790</v>
       </c>
       <c r="D2" t="n">
-        <v>29297</v>
+        <v>14986</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2090</v>
+        <v>1904</v>
       </c>
       <c r="C3" t="n">
-        <v>3503</v>
+        <v>2043</v>
       </c>
       <c r="D3" t="n">
-        <v>2032</v>
+        <v>2296</v>
       </c>
     </row>
     <row r="4">
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5283</v>
+        <v>5979</v>
       </c>
       <c r="C2" t="n">
-        <v>7781</v>
+        <v>4779</v>
       </c>
       <c r="D2" t="n">
-        <v>24322</v>
+        <v>17634</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3943</v>
+        <v>3748</v>
       </c>
       <c r="C3" t="n">
-        <v>4822</v>
+        <v>3617</v>
       </c>
       <c r="D3" t="n">
-        <v>6462</v>
+        <v>4258</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>942</v>
+        <v>860</v>
       </c>
       <c r="C4" t="n">
-        <v>2096</v>
+        <v>1259</v>
       </c>
       <c r="D4" t="n">
-        <v>1590</v>
+        <v>1644</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C5" t="n">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="D5" t="n">
-        <v>1198</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C6" t="n">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="D6" t="n">
-        <v>853</v>
+        <v>864</v>
       </c>
     </row>
     <row r="7">
@@ -4893,7 +4893,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C7" t="n">
         <v>409</v>
@@ -4921,10 +4921,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C9" t="n">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="D9" t="n">
         <v>363</v>
@@ -4935,7 +4935,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C10" t="n">
         <v>192</v>
@@ -4949,10 +4949,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C11" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D11" t="n">
         <v>270</v>
@@ -4983,7 +4983,7 @@
         <v>103</v>
       </c>
       <c r="D13" t="n">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="14">
@@ -4997,7 +4997,7 @@
         <v>83</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15">
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C15" t="n">
         <v>74</v>
@@ -5025,7 +5025,7 @@
         <v>71</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="17">
@@ -5036,10 +5036,10 @@
         <v>12</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5367</v>
+        <v>5275</v>
       </c>
       <c r="C2" t="n">
-        <v>13192</v>
+        <v>6261</v>
       </c>
       <c r="D2" t="n">
-        <v>20053</v>
+        <v>16491</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3784</v>
+        <v>3972</v>
       </c>
       <c r="C3" t="n">
-        <v>5570</v>
+        <v>3679</v>
       </c>
       <c r="D3" t="n">
-        <v>8854</v>
+        <v>6091</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2071</v>
+        <v>1945</v>
       </c>
       <c r="C4" t="n">
-        <v>3596</v>
+        <v>2556</v>
       </c>
       <c r="D4" t="n">
-        <v>2477</v>
+        <v>2095</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>439</v>
+        <v>414</v>
       </c>
       <c r="C5" t="n">
-        <v>1243</v>
+        <v>793</v>
       </c>
       <c r="D5" t="n">
-        <v>1221</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C6" t="n">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="D6" t="n">
-        <v>903</v>
+        <v>910</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C7" t="n">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>629</v>
+        <v>625</v>
       </c>
     </row>
     <row r="8">
@@ -5224,7 +5224,7 @@
         <v>358</v>
       </c>
       <c r="D8" t="n">
-        <v>456</v>
+        <v>462</v>
       </c>
     </row>
     <row r="9">
@@ -5232,10 +5232,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C9" t="n">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="D9" t="n">
         <v>372</v>
@@ -5260,10 +5260,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C11" t="n">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="D11" t="n">
         <v>280</v>
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C12" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D12" t="n">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="13">
@@ -5291,7 +5291,7 @@
         <v>21</v>
       </c>
       <c r="C13" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D13" t="n">
         <v>173</v>
@@ -5308,7 +5308,7 @@
         <v>91</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C15" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="16">
@@ -5336,7 +5336,7 @@
         <v>72</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17">
@@ -5350,7 +5350,7 @@
         <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18">
@@ -5361,7 +5361,7 @@
         <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D18" t="n">
         <v>59</v>
@@ -5375,7 +5375,7 @@
         <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D19" t="n">
         <v>41</v>
@@ -5406,7 +5406,7 @@
         <v>122</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5439</v>
+        <v>5552</v>
       </c>
       <c r="C2" t="n">
-        <v>9256</v>
+        <v>3190</v>
       </c>
       <c r="D2" t="n">
-        <v>19181</v>
+        <v>14649</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3715</v>
+        <v>3776</v>
       </c>
       <c r="C3" t="n">
-        <v>8262</v>
+        <v>4373</v>
       </c>
       <c r="D3" t="n">
-        <v>9932</v>
+        <v>7242</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2453</v>
+        <v>2485</v>
       </c>
       <c r="C4" t="n">
-        <v>4582</v>
+        <v>3117</v>
       </c>
       <c r="D4" t="n">
-        <v>3564</v>
+        <v>2740</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1025</v>
+        <v>976</v>
       </c>
       <c r="C5" t="n">
-        <v>2436</v>
+        <v>1707</v>
       </c>
       <c r="D5" t="n">
-        <v>1389</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="C6" t="n">
-        <v>766</v>
+        <v>546</v>
       </c>
       <c r="D6" t="n">
-        <v>945</v>
+        <v>942</v>
       </c>
     </row>
     <row r="7">
@@ -5521,7 +5521,7 @@
         <v>354</v>
       </c>
       <c r="D7" t="n">
-        <v>662</v>
+        <v>668</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C8" t="n">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="D8" t="n">
-        <v>480</v>
+        <v>484</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C9" t="n">
         <v>306</v>
       </c>
       <c r="D9" t="n">
-        <v>381</v>
+        <v>378</v>
       </c>
     </row>
     <row r="10">
@@ -5560,10 +5560,10 @@
         <v>70</v>
       </c>
       <c r="C10" t="n">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D10" t="n">
-        <v>342</v>
+        <v>346</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C11" t="n">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="D11" t="n">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C12" t="n">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D12" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="13">
@@ -5619,7 +5619,7 @@
         <v>100</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="15">
@@ -5630,10 +5630,10 @@
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="16">
@@ -5647,7 +5647,7 @@
         <v>73</v>
       </c>
       <c r="D16" t="n">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17">
@@ -5661,7 +5661,7 @@
         <v>69</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="18">
@@ -5672,7 +5672,7 @@
         <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D18" t="n">
         <v>60</v>
@@ -5700,7 +5700,7 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D20" t="n">
         <v>24</v>
@@ -5717,7 +5717,7 @@
         <v>137</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6435</v>
+        <v>5988</v>
       </c>
       <c r="C2" t="n">
-        <v>7969</v>
+        <v>2659</v>
       </c>
       <c r="D2" t="n">
-        <v>29941</v>
+        <v>17110</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3311</v>
+        <v>3391</v>
       </c>
       <c r="C3" t="n">
-        <v>7181</v>
+        <v>3075</v>
       </c>
       <c r="D3" t="n">
-        <v>10009</v>
+        <v>7393</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1915</v>
+        <v>1942</v>
       </c>
       <c r="C4" t="n">
-        <v>5345</v>
+        <v>3111</v>
       </c>
       <c r="D4" t="n">
-        <v>4027</v>
+        <v>3010</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>894</v>
+        <v>908</v>
       </c>
       <c r="C5" t="n">
-        <v>2593</v>
+        <v>1804</v>
       </c>
       <c r="D5" t="n">
-        <v>1384</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>300</v>
+        <v>289</v>
       </c>
       <c r="C6" t="n">
-        <v>1066</v>
+        <v>770</v>
       </c>
       <c r="D6" t="n">
-        <v>776</v>
+        <v>762</v>
       </c>
     </row>
     <row r="7">
@@ -5829,10 +5829,10 @@
         <v>87</v>
       </c>
       <c r="C7" t="n">
-        <v>355</v>
+        <v>286</v>
       </c>
       <c r="D7" t="n">
-        <v>514</v>
+        <v>525</v>
       </c>
     </row>
     <row r="8">
@@ -5840,10 +5840,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D8" t="n">
         <v>361</v>
@@ -5857,10 +5857,10 @@
         <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="D9" t="n">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C10" t="n">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D10" t="n">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="11">
@@ -5885,10 +5885,10 @@
         <v>21</v>
       </c>
       <c r="C11" t="n">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D11" t="n">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="12">
@@ -5899,10 +5899,10 @@
         <v>14</v>
       </c>
       <c r="C12" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D12" t="n">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="13">
@@ -5913,10 +5913,10 @@
         <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D13" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="14">
@@ -5927,10 +5927,10 @@
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D14" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15">
@@ -5972,7 +5972,7 @@
         <v>35</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -5983,7 +5983,7 @@
         <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
         <v>38</v>
@@ -6011,7 +6011,7 @@
         <v>2</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>15</v>
@@ -6025,10 +6025,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5525</v>
+        <v>5255</v>
       </c>
       <c r="C2" t="n">
-        <v>4151</v>
+        <v>3486</v>
       </c>
       <c r="D2" t="n">
-        <v>32308</v>
+        <v>26432</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4031</v>
+        <v>3915</v>
       </c>
       <c r="C3" t="n">
-        <v>6572</v>
+        <v>2415</v>
       </c>
       <c r="D3" t="n">
-        <v>12620</v>
+        <v>8547</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2282</v>
+        <v>2337</v>
       </c>
       <c r="C4" t="n">
-        <v>6326</v>
+        <v>3023</v>
       </c>
       <c r="D4" t="n">
-        <v>5110</v>
+        <v>3844</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1237</v>
+        <v>1288</v>
       </c>
       <c r="C5" t="n">
-        <v>4099</v>
+        <v>2556</v>
       </c>
       <c r="D5" t="n">
-        <v>1836</v>
+        <v>1564</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>551</v>
+        <v>564</v>
       </c>
       <c r="C6" t="n">
-        <v>1917</v>
+        <v>1365</v>
       </c>
       <c r="D6" t="n">
-        <v>881</v>
+        <v>852</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C7" t="n">
-        <v>752</v>
+        <v>565</v>
       </c>
       <c r="D7" t="n">
-        <v>552</v>
+        <v>566</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C8" t="n">
-        <v>294</v>
+        <v>258</v>
       </c>
       <c r="D8" t="n">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C9" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D9" t="n">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C10" t="n">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="D10" t="n">
-        <v>236</v>
+        <v>240</v>
       </c>
     </row>
     <row r="11">
@@ -6196,10 +6196,10 @@
         <v>23</v>
       </c>
       <c r="C11" t="n">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D11" t="n">
-        <v>199</v>
+        <v>196</v>
       </c>
     </row>
     <row r="12">
@@ -6210,10 +6210,10 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="D12" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="13">
@@ -6224,7 +6224,7 @@
         <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D13" t="n">
         <v>119</v>
@@ -6238,10 +6238,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15">
@@ -6252,7 +6252,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D15" t="n">
         <v>80</v>
@@ -6269,7 +6269,7 @@
         <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -6311,7 +6311,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -6322,10 +6322,10 @@
         <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21">
@@ -6336,10 +6336,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4195</v>
+        <v>5958</v>
       </c>
       <c r="C2" t="n">
-        <v>7981</v>
+        <v>2542</v>
       </c>
       <c r="D2" t="n">
-        <v>31409</v>
+        <v>23838</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3907</v>
+        <v>3778</v>
       </c>
       <c r="C3" t="n">
-        <v>4605</v>
+        <v>2605</v>
       </c>
       <c r="D3" t="n">
-        <v>14724</v>
+        <v>10922</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2698</v>
+        <v>2716</v>
       </c>
       <c r="C4" t="n">
-        <v>6268</v>
+        <v>2604</v>
       </c>
       <c r="D4" t="n">
-        <v>6275</v>
+        <v>4675</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1523</v>
+        <v>1594</v>
       </c>
       <c r="C5" t="n">
-        <v>5210</v>
+        <v>2742</v>
       </c>
       <c r="D5" t="n">
-        <v>2377</v>
+        <v>1954</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>804</v>
+        <v>852</v>
       </c>
       <c r="C6" t="n">
-        <v>3026</v>
+        <v>2011</v>
       </c>
       <c r="D6" t="n">
-        <v>1025</v>
+        <v>961</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>312</v>
+        <v>327</v>
       </c>
       <c r="C7" t="n">
-        <v>1338</v>
+        <v>1003</v>
       </c>
       <c r="D7" t="n">
-        <v>604</v>
+        <v>613</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="C8" t="n">
-        <v>522</v>
+        <v>420</v>
       </c>
       <c r="D8" t="n">
-        <v>405</v>
+        <v>408</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C9" t="n">
-        <v>250</v>
+        <v>234</v>
       </c>
       <c r="D9" t="n">
-        <v>297</v>
+        <v>300</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C10" t="n">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="D10" t="n">
-        <v>241</v>
+        <v>245</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="D11" t="n">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="D12" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D13" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="14">
@@ -6549,10 +6549,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
@@ -6563,7 +6563,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D15" t="n">
         <v>81</v>
@@ -6580,7 +6580,7 @@
         <v>43</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -6605,10 +6605,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19">
@@ -6622,7 +6622,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -6633,7 +6633,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -6647,10 +6647,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_population_iteration_94_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_94_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5703</v>
+        <v>7195</v>
       </c>
       <c r="C2" t="n">
-        <v>4281</v>
+        <v>9528</v>
       </c>
       <c r="D2" t="n">
-        <v>24445</v>
+        <v>41262</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3961</v>
+        <v>4480</v>
       </c>
       <c r="C3" t="n">
-        <v>2234</v>
+        <v>4427</v>
       </c>
       <c r="D3" t="n">
-        <v>12116</v>
+        <v>17009</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2794</v>
+        <v>3482</v>
       </c>
       <c r="C4" t="n">
-        <v>2525</v>
+        <v>3507</v>
       </c>
       <c r="D4" t="n">
-        <v>5627</v>
+        <v>8958</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1874</v>
+        <v>2116</v>
       </c>
       <c r="C5" t="n">
-        <v>2610</v>
+        <v>2242</v>
       </c>
       <c r="D5" t="n">
-        <v>2390</v>
+        <v>3619</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1111</v>
+        <v>1157</v>
       </c>
       <c r="C6" t="n">
-        <v>2367</v>
+        <v>1718</v>
       </c>
       <c r="D6" t="n">
-        <v>1109</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>513</v>
+        <v>533</v>
       </c>
       <c r="C7" t="n">
-        <v>1506</v>
+        <v>1041</v>
       </c>
       <c r="D7" t="n">
-        <v>668</v>
+        <v>694</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>185</v>
+        <v>204</v>
       </c>
       <c r="C8" t="n">
-        <v>711</v>
+        <v>510</v>
       </c>
       <c r="D8" t="n">
-        <v>437</v>
+        <v>444</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="C9" t="n">
-        <v>323</v>
+        <v>278</v>
       </c>
       <c r="D9" t="n">
-        <v>310</v>
+        <v>304</v>
       </c>
     </row>
     <row r="10">
@@ -895,10 +895,10 @@
         <v>39</v>
       </c>
       <c r="C10" t="n">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="D10" t="n">
-        <v>251</v>
+        <v>248</v>
       </c>
     </row>
     <row r="11">
@@ -909,10 +909,10 @@
         <v>27</v>
       </c>
       <c r="C11" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D11" t="n">
-        <v>200</v>
+        <v>206</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C12" t="n">
         <v>131</v>
       </c>
       <c r="D12" t="n">
-        <v>163</v>
+        <v>158</v>
       </c>
     </row>
     <row r="13">
@@ -940,7 +940,7 @@
         <v>101</v>
       </c>
       <c r="D13" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16">
@@ -979,10 +979,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -993,10 +993,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -1010,7 +1010,7 @@
         <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1049,7 +1049,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D21" t="n">
         <v>9</v>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7086</v>
+        <v>8365</v>
       </c>
       <c r="C2" t="n">
-        <v>8195</v>
+        <v>10464</v>
       </c>
       <c r="D2" t="n">
-        <v>26686</v>
+        <v>48349</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3909</v>
+        <v>4650</v>
       </c>
       <c r="C3" t="n">
-        <v>2835</v>
+        <v>6003</v>
       </c>
       <c r="D3" t="n">
-        <v>13057</v>
+        <v>19331</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2875</v>
+        <v>3361</v>
       </c>
       <c r="C4" t="n">
-        <v>2321</v>
+        <v>3893</v>
       </c>
       <c r="D4" t="n">
-        <v>6523</v>
+        <v>10076</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2027</v>
+        <v>2419</v>
       </c>
       <c r="C5" t="n">
-        <v>2513</v>
+        <v>2781</v>
       </c>
       <c r="D5" t="n">
-        <v>2876</v>
+        <v>4345</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1343</v>
+        <v>1434</v>
       </c>
       <c r="C6" t="n">
-        <v>2435</v>
+        <v>1946</v>
       </c>
       <c r="D6" t="n">
-        <v>1292</v>
+        <v>1752</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>699</v>
+        <v>722</v>
       </c>
       <c r="C7" t="n">
-        <v>1918</v>
+        <v>1342</v>
       </c>
       <c r="D7" t="n">
-        <v>734</v>
+        <v>799</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>290</v>
+        <v>307</v>
       </c>
       <c r="C8" t="n">
-        <v>1069</v>
+        <v>749</v>
       </c>
       <c r="D8" t="n">
-        <v>468</v>
+        <v>471</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="C9" t="n">
-        <v>497</v>
+        <v>377</v>
       </c>
       <c r="D9" t="n">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C10" t="n">
-        <v>259</v>
+        <v>234</v>
       </c>
       <c r="D10" t="n">
-        <v>257</v>
+        <v>250</v>
       </c>
     </row>
     <row r="11">
@@ -1223,7 +1223,7 @@
         <v>183</v>
       </c>
       <c r="D11" t="n">
-        <v>202</v>
+        <v>209</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D12" t="n">
-        <v>166</v>
+        <v>160</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D13" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="14">
@@ -1262,10 +1262,10 @@
         <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D14" t="n">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -1304,7 +1304,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -1321,7 +1321,7 @@
         <v>35</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1360,7 +1360,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D21" t="n">
         <v>10</v>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8298</v>
+        <v>9725</v>
       </c>
       <c r="C2" t="n">
-        <v>8093</v>
+        <v>5993</v>
       </c>
       <c r="D2" t="n">
-        <v>37226</v>
+        <v>38171</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4289</v>
+        <v>5093</v>
       </c>
       <c r="C3" t="n">
-        <v>4638</v>
+        <v>6988</v>
       </c>
       <c r="D3" t="n">
-        <v>14033</v>
+        <v>21777</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2835</v>
+        <v>3320</v>
       </c>
       <c r="C4" t="n">
-        <v>2519</v>
+        <v>4726</v>
       </c>
       <c r="D4" t="n">
-        <v>7391</v>
+        <v>11094</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2122</v>
+        <v>2496</v>
       </c>
       <c r="C5" t="n">
-        <v>2348</v>
+        <v>3187</v>
       </c>
       <c r="D5" t="n">
-        <v>3321</v>
+        <v>5093</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1512</v>
+        <v>1675</v>
       </c>
       <c r="C6" t="n">
-        <v>2446</v>
+        <v>2288</v>
       </c>
       <c r="D6" t="n">
-        <v>1517</v>
+        <v>2085</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>872</v>
+        <v>917</v>
       </c>
       <c r="C7" t="n">
-        <v>2126</v>
+        <v>1582</v>
       </c>
       <c r="D7" t="n">
-        <v>801</v>
+        <v>930</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>406</v>
+        <v>416</v>
       </c>
       <c r="C8" t="n">
-        <v>1434</v>
+        <v>992</v>
       </c>
       <c r="D8" t="n">
-        <v>502</v>
+        <v>506</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="C9" t="n">
-        <v>727</v>
+        <v>518</v>
       </c>
       <c r="D9" t="n">
-        <v>335</v>
+        <v>338</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C10" t="n">
-        <v>354</v>
+        <v>288</v>
       </c>
       <c r="D10" t="n">
-        <v>263</v>
+        <v>254</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C11" t="n">
-        <v>210</v>
+        <v>199</v>
       </c>
       <c r="D11" t="n">
-        <v>204</v>
+        <v>212</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="D12" t="n">
-        <v>168</v>
+        <v>162</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D13" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="14">
@@ -1573,10 +1573,10 @@
         <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D14" t="n">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15">
@@ -1587,7 +1587,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D15" t="n">
         <v>83</v>
@@ -1601,7 +1601,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D16" t="n">
         <v>66</v>
@@ -1615,7 +1615,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -1629,10 +1629,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1643,7 +1643,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D19" t="n">
         <v>27</v>
@@ -1671,7 +1671,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D21" t="n">
         <v>11</v>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7454</v>
+        <v>8834</v>
       </c>
       <c r="C2" t="n">
-        <v>5244</v>
+        <v>3979</v>
       </c>
       <c r="D2" t="n">
-        <v>29589</v>
+        <v>31067</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5265</v>
+        <v>6126</v>
       </c>
       <c r="C3" t="n">
-        <v>6601</v>
+        <v>9383</v>
       </c>
       <c r="D3" t="n">
-        <v>15791</v>
+        <v>23676</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1960</v>
+        <v>2306</v>
       </c>
       <c r="C4" t="n">
-        <v>3753</v>
+        <v>5736</v>
       </c>
       <c r="D4" t="n">
-        <v>7198</v>
+        <v>10820</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1397</v>
+        <v>1547</v>
       </c>
       <c r="C5" t="n">
-        <v>2397</v>
+        <v>2242</v>
       </c>
       <c r="D5" t="n">
-        <v>2443</v>
+        <v>3461</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>805</v>
+        <v>847</v>
       </c>
       <c r="C6" t="n">
-        <v>2083</v>
+        <v>1550</v>
       </c>
       <c r="D6" t="n">
-        <v>784</v>
+        <v>911</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>375</v>
+        <v>384</v>
       </c>
       <c r="C7" t="n">
-        <v>1405</v>
+        <v>972</v>
       </c>
       <c r="D7" t="n">
-        <v>491</v>
+        <v>495</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="C8" t="n">
-        <v>712</v>
+        <v>507</v>
       </c>
       <c r="D8" t="n">
-        <v>328</v>
+        <v>331</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C9" t="n">
-        <v>346</v>
+        <v>282</v>
       </c>
       <c r="D9" t="n">
-        <v>257</v>
+        <v>248</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C10" t="n">
-        <v>205</v>
+        <v>195</v>
       </c>
       <c r="D10" t="n">
-        <v>199</v>
+        <v>207</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="D11" t="n">
-        <v>164</v>
+        <v>158</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D12" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="13">
@@ -1870,10 +1870,10 @@
         <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="14">
@@ -1884,7 +1884,7 @@
         <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D14" t="n">
         <v>81</v>
@@ -1898,7 +1898,7 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D15" t="n">
         <v>64</v>
@@ -1912,7 +1912,7 @@
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D16" t="n">
         <v>50</v>
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D17" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18">
@@ -1940,7 +1940,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D18" t="n">
         <v>26</v>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4602</v>
+        <v>5421</v>
       </c>
       <c r="C2" t="n">
-        <v>2539</v>
+        <v>2096</v>
       </c>
       <c r="D2" t="n">
-        <v>21667</v>
+        <v>21793</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5390</v>
+        <v>6290</v>
       </c>
       <c r="C3" t="n">
-        <v>5349</v>
+        <v>6190</v>
       </c>
       <c r="D3" t="n">
-        <v>16843</v>
+        <v>23565</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2862</v>
+        <v>3280</v>
       </c>
       <c r="C4" t="n">
-        <v>5240</v>
+        <v>7587</v>
       </c>
       <c r="D4" t="n">
-        <v>8519</v>
+        <v>12673</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1551</v>
+        <v>1725</v>
       </c>
       <c r="C5" t="n">
-        <v>3061</v>
+        <v>3778</v>
       </c>
       <c r="D5" t="n">
-        <v>3054</v>
+        <v>4340</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>974</v>
+        <v>1032</v>
       </c>
       <c r="C6" t="n">
-        <v>2305</v>
+        <v>1874</v>
       </c>
       <c r="D6" t="n">
-        <v>972</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C7" t="n">
-        <v>1734</v>
+        <v>1221</v>
       </c>
       <c r="D7" t="n">
-        <v>534</v>
+        <v>543</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="C8" t="n">
-        <v>948</v>
+        <v>660</v>
       </c>
       <c r="D8" t="n">
-        <v>349</v>
+        <v>346</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C9" t="n">
-        <v>416</v>
+        <v>336</v>
       </c>
       <c r="D9" t="n">
-        <v>265</v>
+        <v>260</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="D10" t="n">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="D11" t="n">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="12">
@@ -2167,10 +2167,10 @@
         <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D12" t="n">
-        <v>133</v>
+        <v>130</v>
       </c>
     </row>
     <row r="13">
@@ -2181,7 +2181,7 @@
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D13" t="n">
         <v>101</v>
@@ -2195,7 +2195,7 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D14" t="n">
         <v>62</v>
@@ -2209,7 +2209,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D15" t="n">
         <v>49</v>
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D16" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17">
@@ -2237,7 +2237,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D17" t="n">
         <v>25</v>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4689</v>
+        <v>6876</v>
       </c>
       <c r="C2" t="n">
-        <v>8621</v>
+        <v>5513</v>
       </c>
       <c r="D2" t="n">
-        <v>20406</v>
+        <v>22118</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4219</v>
+        <v>4962</v>
       </c>
       <c r="C3" t="n">
-        <v>3448</v>
+        <v>3681</v>
       </c>
       <c r="D3" t="n">
-        <v>16552</v>
+        <v>21688</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3480</v>
+        <v>3981</v>
       </c>
       <c r="C4" t="n">
-        <v>5188</v>
+        <v>6791</v>
       </c>
       <c r="D4" t="n">
-        <v>9616</v>
+        <v>14169</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1898</v>
+        <v>2121</v>
       </c>
       <c r="C5" t="n">
-        <v>4135</v>
+        <v>5527</v>
       </c>
       <c r="D5" t="n">
-        <v>3905</v>
+        <v>5568</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1143</v>
+        <v>1219</v>
       </c>
       <c r="C6" t="n">
-        <v>2666</v>
+        <v>2750</v>
       </c>
       <c r="D6" t="n">
-        <v>1298</v>
+        <v>1642</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>543</v>
+        <v>560</v>
       </c>
       <c r="C7" t="n">
-        <v>1996</v>
+        <v>1508</v>
       </c>
       <c r="D7" t="n">
-        <v>602</v>
+        <v>629</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="C8" t="n">
-        <v>1303</v>
+        <v>902</v>
       </c>
       <c r="D8" t="n">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C9" t="n">
-        <v>642</v>
+        <v>469</v>
       </c>
       <c r="D9" t="n">
-        <v>272</v>
+        <v>267</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C10" t="n">
-        <v>301</v>
+        <v>264</v>
       </c>
       <c r="D10" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="D11" t="n">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="12">
@@ -2478,10 +2478,10 @@
         <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="D12" t="n">
-        <v>135</v>
+        <v>132</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="D13" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="14">
@@ -2506,7 +2506,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
         <v>65</v>
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D16" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D17" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18">
@@ -2562,7 +2562,7 @@
         <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D18" t="n">
         <v>13</v>
@@ -2576,7 +2576,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D19" t="n">
         <v>7</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2718</v>
+        <v>4030</v>
       </c>
       <c r="C2" t="n">
-        <v>3767</v>
+        <v>2490</v>
       </c>
       <c r="D2" t="n">
-        <v>13943</v>
+        <v>15275</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4183</v>
+        <v>5243</v>
       </c>
       <c r="C3" t="n">
-        <v>5224</v>
+        <v>4202</v>
       </c>
       <c r="D3" t="n">
-        <v>16590</v>
+        <v>21215</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3874</v>
+        <v>4398</v>
       </c>
       <c r="C4" t="n">
-        <v>4943</v>
+        <v>6226</v>
       </c>
       <c r="D4" t="n">
-        <v>10517</v>
+        <v>15140</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2015</v>
+        <v>2206</v>
       </c>
       <c r="C5" t="n">
-        <v>4959</v>
+        <v>6606</v>
       </c>
       <c r="D5" t="n">
-        <v>4337</v>
+        <v>6050</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>998</v>
+        <v>1024</v>
       </c>
       <c r="C6" t="n">
-        <v>3484</v>
+        <v>3416</v>
       </c>
       <c r="D6" t="n">
-        <v>1280</v>
+        <v>1596</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="C7" t="n">
-        <v>2218</v>
+        <v>1611</v>
       </c>
       <c r="D7" t="n">
-        <v>610</v>
+        <v>625</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>1076</v>
+        <v>751</v>
       </c>
       <c r="D8" t="n">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C9" t="n">
-        <v>294</v>
+        <v>258</v>
       </c>
       <c r="D9" t="n">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="D10" t="n">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="11">
@@ -2775,10 +2775,10 @@
         <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="D11" t="n">
-        <v>132</v>
+        <v>129</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="D12" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="13">
@@ -2803,7 +2803,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D13" t="n">
         <v>63</v>
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D14" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D15" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D16" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="17">
@@ -2859,7 +2859,7 @@
         <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D17" t="n">
         <v>12</v>
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D18" t="n">
         <v>6</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4305</v>
+        <v>4831</v>
       </c>
       <c r="C2" t="n">
-        <v>7355</v>
+        <v>2388</v>
       </c>
       <c r="D2" t="n">
-        <v>13041</v>
+        <v>15722</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3023</v>
+        <v>4034</v>
       </c>
       <c r="C3" t="n">
-        <v>3984</v>
+        <v>2992</v>
       </c>
       <c r="D3" t="n">
-        <v>15067</v>
+        <v>18981</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3510</v>
+        <v>4147</v>
       </c>
       <c r="C4" t="n">
-        <v>5030</v>
+        <v>5165</v>
       </c>
       <c r="D4" t="n">
-        <v>11246</v>
+        <v>15671</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2497</v>
+        <v>2752</v>
       </c>
       <c r="C5" t="n">
-        <v>4895</v>
+        <v>6356</v>
       </c>
       <c r="D5" t="n">
-        <v>5255</v>
+        <v>7262</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1297</v>
+        <v>1353</v>
       </c>
       <c r="C6" t="n">
-        <v>4149</v>
+        <v>4795</v>
       </c>
       <c r="D6" t="n">
-        <v>1703</v>
+        <v>2231</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>398</v>
+        <v>388</v>
       </c>
       <c r="C7" t="n">
-        <v>2806</v>
+        <v>2384</v>
       </c>
       <c r="D7" t="n">
-        <v>701</v>
+        <v>742</v>
       </c>
     </row>
     <row r="8">
@@ -3041,10 +3041,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C8" t="n">
-        <v>1544</v>
+        <v>1085</v>
       </c>
       <c r="D8" t="n">
         <v>415</v>
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C9" t="n">
-        <v>578</v>
+        <v>429</v>
       </c>
       <c r="D9" t="n">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="10">
@@ -3069,10 +3069,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C10" t="n">
-        <v>229</v>
+        <v>212</v>
       </c>
       <c r="D10" t="n">
         <v>177</v>
@@ -3086,10 +3086,10 @@
         <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="D11" t="n">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="D12" t="n">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="13">
@@ -3114,7 +3114,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D13" t="n">
         <v>63</v>
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
+        <v>46</v>
+      </c>
+      <c r="D14" t="n">
         <v>47</v>
-      </c>
-      <c r="D14" t="n">
-        <v>48</v>
       </c>
     </row>
     <row r="15">
@@ -3156,7 +3156,7 @@
         <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D16" t="n">
         <v>20</v>
@@ -3170,7 +3170,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D17" t="n">
         <v>10</v>
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
         <v>2</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3078</v>
+        <v>3471</v>
       </c>
       <c r="C2" t="n">
-        <v>4730</v>
+        <v>1719</v>
       </c>
       <c r="D2" t="n">
-        <v>9327</v>
+        <v>13093</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3043</v>
+        <v>3762</v>
       </c>
       <c r="C3" t="n">
-        <v>4948</v>
+        <v>2487</v>
       </c>
       <c r="D3" t="n">
-        <v>13963</v>
+        <v>17557</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3088</v>
+        <v>3750</v>
       </c>
       <c r="C4" t="n">
-        <v>4560</v>
+        <v>4288</v>
       </c>
       <c r="D4" t="n">
-        <v>11562</v>
+        <v>15789</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2715</v>
+        <v>3034</v>
       </c>
       <c r="C5" t="n">
-        <v>5035</v>
+        <v>6021</v>
       </c>
       <c r="D5" t="n">
-        <v>5943</v>
+        <v>8149</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1538</v>
+        <v>1606</v>
       </c>
       <c r="C6" t="n">
-        <v>4578</v>
+        <v>5490</v>
       </c>
       <c r="D6" t="n">
-        <v>2056</v>
+        <v>2682</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>415</v>
+        <v>377</v>
       </c>
       <c r="C7" t="n">
-        <v>3379</v>
+        <v>3160</v>
       </c>
       <c r="D7" t="n">
-        <v>798</v>
+        <v>851</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="C8" t="n">
-        <v>1947</v>
+        <v>1409</v>
       </c>
       <c r="D8" t="n">
-        <v>436</v>
+        <v>439</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C9" t="n">
-        <v>724</v>
+        <v>515</v>
       </c>
       <c r="D9" t="n">
-        <v>302</v>
+        <v>298</v>
       </c>
     </row>
     <row r="10">
@@ -3383,7 +3383,7 @@
         <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>240</v>
+        <v>223</v>
       </c>
       <c r="D10" t="n">
         <v>181</v>
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="D11" t="n">
-        <v>140</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="D12" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D13" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14">
@@ -3442,7 +3442,7 @@
         <v>38</v>
       </c>
       <c r="D14" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="15">
@@ -3453,7 +3453,7 @@
         <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D15" t="n">
         <v>19</v>
@@ -3467,7 +3467,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D16" t="n">
         <v>9</v>
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4835</v>
+        <v>5525</v>
       </c>
       <c r="C2" t="n">
-        <v>3819</v>
+        <v>4947</v>
       </c>
       <c r="D2" t="n">
-        <v>13622</v>
+        <v>15823</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2566</v>
+        <v>3074</v>
       </c>
       <c r="C3" t="n">
-        <v>4324</v>
+        <v>1921</v>
       </c>
       <c r="D3" t="n">
-        <v>12453</v>
+        <v>16002</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2668</v>
+        <v>3262</v>
       </c>
       <c r="C4" t="n">
-        <v>4643</v>
+        <v>3403</v>
       </c>
       <c r="D4" t="n">
-        <v>11579</v>
+        <v>15412</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2629</v>
+        <v>3024</v>
       </c>
       <c r="C5" t="n">
-        <v>4720</v>
+        <v>5163</v>
       </c>
       <c r="D5" t="n">
-        <v>6514</v>
+        <v>9001</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1833</v>
+        <v>1950</v>
       </c>
       <c r="C6" t="n">
-        <v>4728</v>
+        <v>5655</v>
       </c>
       <c r="D6" t="n">
-        <v>2588</v>
+        <v>3381</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>716</v>
+        <v>688</v>
       </c>
       <c r="C7" t="n">
-        <v>3904</v>
+        <v>4103</v>
       </c>
       <c r="D7" t="n">
-        <v>962</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>155</v>
+        <v>136</v>
       </c>
       <c r="C8" t="n">
-        <v>2493</v>
+        <v>2043</v>
       </c>
       <c r="D8" t="n">
-        <v>477</v>
+        <v>482</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C9" t="n">
-        <v>1174</v>
+        <v>826</v>
       </c>
       <c r="D9" t="n">
-        <v>317</v>
+        <v>310</v>
       </c>
     </row>
     <row r="10">
@@ -3694,10 +3694,10 @@
         <v>6</v>
       </c>
       <c r="C10" t="n">
-        <v>405</v>
+        <v>316</v>
       </c>
       <c r="D10" t="n">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>175</v>
+        <v>164</v>
       </c>
       <c r="D11" t="n">
-        <v>143</v>
+        <v>138</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D13" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14">
@@ -3753,7 +3753,7 @@
         <v>40</v>
       </c>
       <c r="D14" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15">
@@ -3764,10 +3764,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16">
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D16" t="n">
         <v>8</v>
@@ -3792,7 +3792,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4479</v>
+        <v>6547</v>
       </c>
       <c r="C2" t="n">
-        <v>3991</v>
+        <v>3485</v>
       </c>
       <c r="D2" t="n">
-        <v>9864</v>
+        <v>14624</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3347</v>
+        <v>3912</v>
       </c>
       <c r="C2" t="n">
-        <v>2046</v>
+        <v>2770</v>
       </c>
       <c r="D2" t="n">
-        <v>9917</v>
+        <v>11647</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3500</v>
+        <v>4149</v>
       </c>
       <c r="C3" t="n">
-        <v>4536</v>
+        <v>2810</v>
       </c>
       <c r="D3" t="n">
-        <v>13602</v>
+        <v>17262</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3783</v>
+        <v>4461</v>
       </c>
       <c r="C4" t="n">
-        <v>6393</v>
+        <v>5024</v>
       </c>
       <c r="D4" t="n">
-        <v>11887</v>
+        <v>15981</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1839</v>
+        <v>1913</v>
       </c>
       <c r="C5" t="n">
-        <v>6738</v>
+        <v>7742</v>
       </c>
       <c r="D5" t="n">
-        <v>6057</v>
+        <v>8223</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>661</v>
+        <v>635</v>
       </c>
       <c r="C6" t="n">
-        <v>4937</v>
+        <v>5240</v>
       </c>
       <c r="D6" t="n">
-        <v>2104</v>
+        <v>2562</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>143</v>
+        <v>125</v>
       </c>
       <c r="C7" t="n">
-        <v>2443</v>
+        <v>2002</v>
       </c>
       <c r="D7" t="n">
-        <v>599</v>
+        <v>619</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C8" t="n">
-        <v>1150</v>
+        <v>809</v>
       </c>
       <c r="D8" t="n">
-        <v>310</v>
+        <v>303</v>
       </c>
     </row>
     <row r="9">
@@ -4302,10 +4302,10 @@
         <v>5</v>
       </c>
       <c r="C9" t="n">
-        <v>396</v>
+        <v>309</v>
       </c>
       <c r="D9" t="n">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>171</v>
+        <v>160</v>
       </c>
       <c r="D10" t="n">
-        <v>140</v>
+        <v>135</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="D11" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D12" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13">
@@ -4361,7 +4361,7 @@
         <v>39</v>
       </c>
       <c r="D13" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14">
@@ -4372,10 +4372,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D14" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15">
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D15" t="n">
         <v>7</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7240</v>
+        <v>6985</v>
       </c>
       <c r="C2" t="n">
-        <v>5790</v>
+        <v>2533</v>
       </c>
       <c r="D2" t="n">
-        <v>14986</v>
+        <v>29297</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1904</v>
+        <v>2781</v>
       </c>
       <c r="C3" t="n">
-        <v>2043</v>
+        <v>1756</v>
       </c>
       <c r="D3" t="n">
-        <v>2296</v>
+        <v>3096</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>79</v>
       </c>
       <c r="C4" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D4" t="n">
         <v>1538</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C5" t="n">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="D5" t="n">
         <v>1161</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C6" t="n">
         <v>459</v>
       </c>
       <c r="D6" t="n">
-        <v>808</v>
+        <v>816</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>350</v>
       </c>
       <c r="D7" t="n">
-        <v>546</v>
+        <v>538</v>
       </c>
     </row>
     <row r="8">
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5979</v>
+        <v>4617</v>
       </c>
       <c r="C2" t="n">
-        <v>4779</v>
+        <v>4919</v>
       </c>
       <c r="D2" t="n">
-        <v>17634</v>
+        <v>29445</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3748</v>
+        <v>4010</v>
       </c>
       <c r="C3" t="n">
-        <v>3617</v>
+        <v>1893</v>
       </c>
       <c r="D3" t="n">
-        <v>4258</v>
+        <v>7269</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>860</v>
+        <v>1242</v>
       </c>
       <c r="C4" t="n">
-        <v>1259</v>
+        <v>1074</v>
       </c>
       <c r="D4" t="n">
-        <v>1644</v>
+        <v>1805</v>
       </c>
     </row>
     <row r="5">
@@ -4868,10 +4868,10 @@
         <v>125</v>
       </c>
       <c r="C5" t="n">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D5" t="n">
-        <v>1186</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C6" t="n">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="D6" t="n">
-        <v>864</v>
+        <v>859</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="C7" t="n">
         <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>589</v>
+        <v>584</v>
       </c>
     </row>
     <row r="8">
@@ -4913,7 +4913,7 @@
         <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="9">
@@ -4921,10 +4921,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C9" t="n">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="D9" t="n">
         <v>363</v>
@@ -4935,7 +4935,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C10" t="n">
         <v>192</v>
@@ -4949,10 +4949,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D11" t="n">
         <v>270</v>
@@ -4983,7 +4983,7 @@
         <v>103</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="14">
@@ -4997,7 +4997,7 @@
         <v>83</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="15">
@@ -5036,7 +5036,7 @@
         <v>12</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D17" t="n">
         <v>78</v>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5275</v>
+        <v>6099</v>
       </c>
       <c r="C2" t="n">
-        <v>6261</v>
+        <v>3433</v>
       </c>
       <c r="D2" t="n">
-        <v>16491</v>
+        <v>27429</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3972</v>
+        <v>3552</v>
       </c>
       <c r="C3" t="n">
-        <v>3679</v>
+        <v>3066</v>
       </c>
       <c r="D3" t="n">
-        <v>6091</v>
+        <v>10293</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1945</v>
+        <v>2234</v>
       </c>
       <c r="C4" t="n">
-        <v>2556</v>
+        <v>1515</v>
       </c>
       <c r="D4" t="n">
-        <v>2095</v>
+        <v>2799</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>414</v>
+        <v>559</v>
       </c>
       <c r="C5" t="n">
-        <v>793</v>
+        <v>682</v>
       </c>
       <c r="D5" t="n">
-        <v>1222</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C6" t="n">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="D6" t="n">
-        <v>910</v>
+        <v>908</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C7" t="n">
         <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>625</v>
+        <v>620</v>
       </c>
     </row>
     <row r="8">
@@ -5224,7 +5224,7 @@
         <v>358</v>
       </c>
       <c r="D8" t="n">
-        <v>462</v>
+        <v>460</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C9" t="n">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="D9" t="n">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="10">
@@ -5249,7 +5249,7 @@
         <v>66</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D10" t="n">
         <v>346</v>
@@ -5260,10 +5260,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C11" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D11" t="n">
         <v>280</v>
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C12" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D12" t="n">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="13">
@@ -5291,7 +5291,7 @@
         <v>21</v>
       </c>
       <c r="C13" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D13" t="n">
         <v>173</v>
@@ -5305,10 +5305,10 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15">
@@ -5322,7 +5322,7 @@
         <v>77</v>
       </c>
       <c r="D15" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16">
@@ -5361,7 +5361,7 @@
         <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
         <v>59</v>
@@ -5375,7 +5375,7 @@
         <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D19" t="n">
         <v>41</v>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5552</v>
+        <v>6599</v>
       </c>
       <c r="C2" t="n">
-        <v>3190</v>
+        <v>3702</v>
       </c>
       <c r="D2" t="n">
-        <v>14649</v>
+        <v>32280</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3776</v>
+        <v>3897</v>
       </c>
       <c r="C3" t="n">
-        <v>4373</v>
+        <v>2833</v>
       </c>
       <c r="D3" t="n">
-        <v>7242</v>
+        <v>12173</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2485</v>
+        <v>2469</v>
       </c>
       <c r="C4" t="n">
-        <v>3117</v>
+        <v>2302</v>
       </c>
       <c r="D4" t="n">
-        <v>2740</v>
+        <v>4053</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>976</v>
+        <v>1145</v>
       </c>
       <c r="C5" t="n">
-        <v>1707</v>
+        <v>1107</v>
       </c>
       <c r="D5" t="n">
-        <v>1344</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>245</v>
+        <v>305</v>
       </c>
       <c r="C6" t="n">
-        <v>546</v>
+        <v>491</v>
       </c>
       <c r="D6" t="n">
-        <v>942</v>
+        <v>956</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C7" t="n">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="D7" t="n">
-        <v>668</v>
+        <v>655</v>
       </c>
     </row>
     <row r="8">
@@ -5535,7 +5535,7 @@
         <v>382</v>
       </c>
       <c r="D8" t="n">
-        <v>484</v>
+        <v>481</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C9" t="n">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="D9" t="n">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="10">
@@ -5560,7 +5560,7 @@
         <v>70</v>
       </c>
       <c r="C10" t="n">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="D10" t="n">
         <v>346</v>
@@ -5574,10 +5574,10 @@
         <v>50</v>
       </c>
       <c r="C11" t="n">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D11" t="n">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="12">
@@ -5588,10 +5588,10 @@
         <v>33</v>
       </c>
       <c r="C12" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D12" t="n">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="13">
@@ -5602,7 +5602,7 @@
         <v>22</v>
       </c>
       <c r="C13" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D13" t="n">
         <v>176</v>
@@ -5619,7 +5619,7 @@
         <v>100</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15">
@@ -5630,10 +5630,10 @@
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D15" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="16">
@@ -5647,7 +5647,7 @@
         <v>73</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17">
@@ -5658,10 +5658,10 @@
         <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18">
@@ -5672,7 +5672,7 @@
         <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
         <v>60</v>
@@ -5700,7 +5700,7 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D20" t="n">
         <v>24</v>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5988</v>
+        <v>8015</v>
       </c>
       <c r="C2" t="n">
-        <v>2659</v>
+        <v>3409</v>
       </c>
       <c r="D2" t="n">
-        <v>17110</v>
+        <v>26279</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3391</v>
+        <v>3807</v>
       </c>
       <c r="C3" t="n">
-        <v>3075</v>
+        <v>2689</v>
       </c>
       <c r="D3" t="n">
-        <v>7393</v>
+        <v>13521</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1942</v>
+        <v>1988</v>
       </c>
       <c r="C4" t="n">
-        <v>3111</v>
+        <v>2132</v>
       </c>
       <c r="D4" t="n">
-        <v>3010</v>
+        <v>4688</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>908</v>
+        <v>944</v>
       </c>
       <c r="C5" t="n">
-        <v>1804</v>
+        <v>1272</v>
       </c>
       <c r="D5" t="n">
-        <v>1263</v>
+        <v>1558</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>289</v>
+        <v>346</v>
       </c>
       <c r="C6" t="n">
-        <v>770</v>
+        <v>537</v>
       </c>
       <c r="D6" t="n">
-        <v>762</v>
+        <v>791</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="C7" t="n">
-        <v>286</v>
+        <v>269</v>
       </c>
       <c r="D7" t="n">
-        <v>525</v>
+        <v>518</v>
       </c>
     </row>
     <row r="8">
@@ -5843,7 +5843,7 @@
         <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="D8" t="n">
         <v>361</v>
@@ -5857,10 +5857,10 @@
         <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D9" t="n">
-        <v>273</v>
+        <v>269</v>
       </c>
     </row>
     <row r="10">
@@ -5868,10 +5868,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C10" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D10" t="n">
         <v>237</v>
@@ -5885,10 +5885,10 @@
         <v>21</v>
       </c>
       <c r="C11" t="n">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D11" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="12">
@@ -5899,10 +5899,10 @@
         <v>14</v>
       </c>
       <c r="C12" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D12" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="13">
@@ -5913,7 +5913,7 @@
         <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D13" t="n">
         <v>116</v>
@@ -5927,7 +5927,7 @@
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D14" t="n">
         <v>97</v>
@@ -5958,7 +5958,7 @@
         <v>38</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -5972,7 +5972,7 @@
         <v>35</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18">
@@ -5980,7 +5980,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
         <v>33</v>
@@ -6025,7 +6025,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D21" t="n">
         <v>6</v>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5255</v>
+        <v>7004</v>
       </c>
       <c r="C2" t="n">
-        <v>3486</v>
+        <v>7144</v>
       </c>
       <c r="D2" t="n">
-        <v>26432</v>
+        <v>26996</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3915</v>
+        <v>4986</v>
       </c>
       <c r="C3" t="n">
-        <v>2415</v>
+        <v>2674</v>
       </c>
       <c r="D3" t="n">
-        <v>8547</v>
+        <v>14749</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2337</v>
+        <v>2532</v>
       </c>
       <c r="C4" t="n">
-        <v>3023</v>
+        <v>2429</v>
       </c>
       <c r="D4" t="n">
-        <v>3844</v>
+        <v>6411</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1288</v>
+        <v>1316</v>
       </c>
       <c r="C5" t="n">
-        <v>2556</v>
+        <v>1757</v>
       </c>
       <c r="D5" t="n">
-        <v>1564</v>
+        <v>2141</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>564</v>
+        <v>599</v>
       </c>
       <c r="C6" t="n">
-        <v>1365</v>
+        <v>948</v>
       </c>
       <c r="D6" t="n">
-        <v>852</v>
+        <v>919</v>
       </c>
     </row>
     <row r="7">
@@ -6137,10 +6137,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>172</v>
+        <v>204</v>
       </c>
       <c r="C7" t="n">
-        <v>565</v>
+        <v>423</v>
       </c>
       <c r="D7" t="n">
         <v>566</v>
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C8" t="n">
-        <v>258</v>
+        <v>247</v>
       </c>
       <c r="D8" t="n">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C9" t="n">
         <v>211</v>
       </c>
       <c r="D9" t="n">
-        <v>286</v>
+        <v>279</v>
       </c>
     </row>
     <row r="10">
@@ -6179,7 +6179,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C10" t="n">
         <v>176</v>
@@ -6196,10 +6196,10 @@
         <v>23</v>
       </c>
       <c r="C11" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D11" t="n">
-        <v>196</v>
+        <v>199</v>
       </c>
     </row>
     <row r="12">
@@ -6213,7 +6213,7 @@
         <v>103</v>
       </c>
       <c r="D12" t="n">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="13">
@@ -6238,10 +6238,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
@@ -6255,7 +6255,7 @@
         <v>50</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -6269,7 +6269,7 @@
         <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -6297,7 +6297,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -6305,7 +6305,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C19" t="n">
         <v>31</v>
@@ -6325,7 +6325,7 @@
         <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21">
@@ -6336,7 +6336,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D21" t="n">
         <v>7</v>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5958</v>
+        <v>6002</v>
       </c>
       <c r="C2" t="n">
-        <v>2542</v>
+        <v>5683</v>
       </c>
       <c r="D2" t="n">
-        <v>23838</v>
+        <v>31866</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3778</v>
+        <v>4925</v>
       </c>
       <c r="C3" t="n">
-        <v>2605</v>
+        <v>4455</v>
       </c>
       <c r="D3" t="n">
-        <v>10922</v>
+        <v>15646</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2716</v>
+        <v>3224</v>
       </c>
       <c r="C4" t="n">
-        <v>2604</v>
+        <v>2519</v>
       </c>
       <c r="D4" t="n">
-        <v>4675</v>
+        <v>7755</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1594</v>
+        <v>1701</v>
       </c>
       <c r="C5" t="n">
-        <v>2742</v>
+        <v>2077</v>
       </c>
       <c r="D5" t="n">
-        <v>1954</v>
+        <v>2895</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>852</v>
+        <v>870</v>
       </c>
       <c r="C6" t="n">
-        <v>2011</v>
+        <v>1379</v>
       </c>
       <c r="D6" t="n">
-        <v>961</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>327</v>
+        <v>360</v>
       </c>
       <c r="C7" t="n">
-        <v>1003</v>
+        <v>705</v>
       </c>
       <c r="D7" t="n">
-        <v>613</v>
+        <v>625</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>106</v>
+        <v>120</v>
       </c>
       <c r="C8" t="n">
-        <v>420</v>
+        <v>338</v>
       </c>
       <c r="D8" t="n">
-        <v>408</v>
+        <v>413</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="D9" t="n">
-        <v>300</v>
+        <v>291</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C10" t="n">
         <v>193</v>
       </c>
       <c r="D10" t="n">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="11">
@@ -6507,10 +6507,10 @@
         <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D11" t="n">
-        <v>198</v>
+        <v>203</v>
       </c>
     </row>
     <row r="12">
@@ -6524,7 +6524,7 @@
         <v>116</v>
       </c>
       <c r="D12" t="n">
-        <v>159</v>
+        <v>155</v>
       </c>
     </row>
     <row r="13">
@@ -6532,7 +6532,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C13" t="n">
         <v>91</v>
@@ -6549,7 +6549,7 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D14" t="n">
         <v>98</v>
@@ -6563,10 +6563,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -6594,7 +6594,7 @@
         <v>37</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -6608,7 +6608,7 @@
         <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -6630,7 +6630,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C20" t="n">
         <v>29</v>
@@ -6647,7 +6647,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D21" t="n">
         <v>8</v>

--- a/output/yearly_population_iteration_94_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_94_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7195</v>
+        <v>1408</v>
       </c>
       <c r="C2" t="n">
-        <v>9528</v>
+        <v>3433</v>
       </c>
       <c r="D2" t="n">
-        <v>41262</v>
+        <v>9440</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4480</v>
+        <v>2319</v>
       </c>
       <c r="C3" t="n">
-        <v>4427</v>
+        <v>7641</v>
       </c>
       <c r="D3" t="n">
-        <v>17009</v>
+        <v>8585</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3482</v>
+        <v>1486</v>
       </c>
       <c r="C4" t="n">
-        <v>3507</v>
+        <v>8743</v>
       </c>
       <c r="D4" t="n">
-        <v>8958</v>
+        <v>4100</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2116</v>
+        <v>711</v>
       </c>
       <c r="C5" t="n">
-        <v>2242</v>
+        <v>6443</v>
       </c>
       <c r="D5" t="n">
-        <v>3619</v>
+        <v>1575</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1157</v>
+        <v>278</v>
       </c>
       <c r="C6" t="n">
-        <v>1718</v>
+        <v>3175</v>
       </c>
       <c r="D6" t="n">
-        <v>1411</v>
+        <v>717</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>533</v>
+        <v>100</v>
       </c>
       <c r="C7" t="n">
-        <v>1041</v>
+        <v>1120</v>
       </c>
       <c r="D7" t="n">
-        <v>694</v>
+        <v>493</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>204</v>
+        <v>72</v>
       </c>
       <c r="C8" t="n">
-        <v>510</v>
+        <v>381</v>
       </c>
       <c r="D8" t="n">
-        <v>444</v>
+        <v>364</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>73</v>
+        <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D9" t="n">
-        <v>304</v>
+        <v>320</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="C10" t="n">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="D10" t="n">
-        <v>248</v>
+        <v>264</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>210</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>131</v>
+        <v>108</v>
       </c>
       <c r="D12" t="n">
-        <v>158</v>
+        <v>174</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>138</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>89</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>71</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>54</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
+        <v>52</v>
+      </c>
+      <c r="D17" t="n">
         <v>38</v>
-      </c>
-      <c r="D17" t="n">
-        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>22</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>140</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8365</v>
+        <v>1725</v>
       </c>
       <c r="C2" t="n">
-        <v>10464</v>
+        <v>6223</v>
       </c>
       <c r="D2" t="n">
-        <v>48349</v>
+        <v>11438</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4650</v>
+        <v>1604</v>
       </c>
       <c r="C3" t="n">
-        <v>6003</v>
+        <v>4765</v>
       </c>
       <c r="D3" t="n">
-        <v>19331</v>
+        <v>8110</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3361</v>
+        <v>1623</v>
       </c>
       <c r="C4" t="n">
-        <v>3893</v>
+        <v>8052</v>
       </c>
       <c r="D4" t="n">
-        <v>10076</v>
+        <v>4793</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2419</v>
+        <v>932</v>
       </c>
       <c r="C5" t="n">
-        <v>2781</v>
+        <v>7479</v>
       </c>
       <c r="D5" t="n">
-        <v>4345</v>
+        <v>1963</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1434</v>
+        <v>420</v>
       </c>
       <c r="C6" t="n">
-        <v>1946</v>
+        <v>4772</v>
       </c>
       <c r="D6" t="n">
-        <v>1752</v>
+        <v>847</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>722</v>
+        <v>155</v>
       </c>
       <c r="C7" t="n">
-        <v>1342</v>
+        <v>2097</v>
       </c>
       <c r="D7" t="n">
-        <v>799</v>
+        <v>527</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>307</v>
+        <v>78</v>
       </c>
       <c r="C8" t="n">
-        <v>749</v>
+        <v>714</v>
       </c>
       <c r="D8" t="n">
-        <v>471</v>
+        <v>377</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>111</v>
+        <v>55</v>
       </c>
       <c r="C9" t="n">
-        <v>377</v>
+        <v>321</v>
       </c>
       <c r="D9" t="n">
-        <v>321</v>
+        <v>325</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="C10" t="n">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="D10" t="n">
-        <v>250</v>
+        <v>267</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="D11" t="n">
-        <v>209</v>
+        <v>215</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>143</v>
+        <v>129</v>
       </c>
       <c r="D12" t="n">
-        <v>160</v>
+        <v>176</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="D13" t="n">
-        <v>127</v>
+        <v>141</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C14" t="n">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>94</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>71</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>94</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>76</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9725</v>
+        <v>927</v>
       </c>
       <c r="C2" t="n">
-        <v>5993</v>
+        <v>2679</v>
       </c>
       <c r="D2" t="n">
-        <v>38171</v>
+        <v>7818</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5093</v>
+        <v>1576</v>
       </c>
       <c r="C3" t="n">
-        <v>6988</v>
+        <v>5130</v>
       </c>
       <c r="D3" t="n">
-        <v>21777</v>
+        <v>8301</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3320</v>
+        <v>1775</v>
       </c>
       <c r="C4" t="n">
-        <v>4726</v>
+        <v>7426</v>
       </c>
       <c r="D4" t="n">
-        <v>11094</v>
+        <v>5227</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2496</v>
+        <v>920</v>
       </c>
       <c r="C5" t="n">
-        <v>3187</v>
+        <v>8595</v>
       </c>
       <c r="D5" t="n">
-        <v>5093</v>
+        <v>2197</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1675</v>
+        <v>325</v>
       </c>
       <c r="C6" t="n">
-        <v>2288</v>
+        <v>5923</v>
       </c>
       <c r="D6" t="n">
-        <v>2085</v>
+        <v>865</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>917</v>
+        <v>72</v>
       </c>
       <c r="C7" t="n">
-        <v>1582</v>
+        <v>1934</v>
       </c>
       <c r="D7" t="n">
-        <v>930</v>
+        <v>552</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>416</v>
+        <v>50</v>
       </c>
       <c r="C8" t="n">
-        <v>992</v>
+        <v>559</v>
       </c>
       <c r="D8" t="n">
-        <v>506</v>
+        <v>434</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>163</v>
+        <v>26</v>
       </c>
       <c r="C9" t="n">
-        <v>518</v>
+        <v>233</v>
       </c>
       <c r="D9" t="n">
-        <v>338</v>
+        <v>360</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>62</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>288</v>
+        <v>185</v>
       </c>
       <c r="D10" t="n">
-        <v>254</v>
+        <v>210</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>199</v>
+        <v>126</v>
       </c>
       <c r="D11" t="n">
-        <v>212</v>
+        <v>172</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>155</v>
+        <v>85</v>
       </c>
       <c r="D12" t="n">
-        <v>162</v>
+        <v>138</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>122</v>
+        <v>67</v>
       </c>
       <c r="D13" t="n">
-        <v>129</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>92</v>
+        <v>62</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>69</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>83</v>
+        <v>51</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="C17" t="n">
-        <v>42</v>
+        <v>92</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>17</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>74</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>112</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8834</v>
+        <v>851</v>
       </c>
       <c r="C2" t="n">
-        <v>3979</v>
+        <v>6740</v>
       </c>
       <c r="D2" t="n">
-        <v>31067</v>
+        <v>10403</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>6126</v>
+        <v>1099</v>
       </c>
       <c r="C3" t="n">
-        <v>9383</v>
+        <v>3444</v>
       </c>
       <c r="D3" t="n">
-        <v>23676</v>
+        <v>7660</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2306</v>
+        <v>1499</v>
       </c>
       <c r="C4" t="n">
-        <v>5736</v>
+        <v>6152</v>
       </c>
       <c r="D4" t="n">
-        <v>10820</v>
+        <v>5599</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1547</v>
+        <v>1142</v>
       </c>
       <c r="C5" t="n">
-        <v>2242</v>
+        <v>7926</v>
       </c>
       <c r="D5" t="n">
-        <v>3461</v>
+        <v>2645</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>847</v>
+        <v>507</v>
       </c>
       <c r="C6" t="n">
-        <v>1550</v>
+        <v>7211</v>
       </c>
       <c r="D6" t="n">
-        <v>911</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>384</v>
+        <v>140</v>
       </c>
       <c r="C7" t="n">
-        <v>972</v>
+        <v>3691</v>
       </c>
       <c r="D7" t="n">
-        <v>495</v>
+        <v>594</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>150</v>
+        <v>54</v>
       </c>
       <c r="C8" t="n">
-        <v>507</v>
+        <v>1108</v>
       </c>
       <c r="D8" t="n">
-        <v>331</v>
+        <v>447</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>57</v>
+        <v>29</v>
       </c>
       <c r="C9" t="n">
-        <v>282</v>
+        <v>354</v>
       </c>
       <c r="D9" t="n">
-        <v>248</v>
+        <v>367</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>195</v>
+        <v>206</v>
       </c>
       <c r="D10" t="n">
-        <v>207</v>
+        <v>223</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="C11" t="n">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="D11" t="n">
-        <v>158</v>
+        <v>176</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>119</v>
+        <v>98</v>
       </c>
       <c r="D12" t="n">
-        <v>126</v>
+        <v>142</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="D13" t="n">
-        <v>98</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
         <v>68</v>
       </c>
       <c r="D14" t="n">
-        <v>81</v>
+        <v>69</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>64</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>41</v>
+        <v>90</v>
       </c>
       <c r="D16" t="n">
-        <v>50</v>
+        <v>31</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>99</v>
       </c>
       <c r="D17" t="n">
-        <v>38</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>112</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5421</v>
+        <v>533</v>
       </c>
       <c r="C2" t="n">
-        <v>2096</v>
+        <v>3432</v>
       </c>
       <c r="D2" t="n">
-        <v>21793</v>
+        <v>7812</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>6290</v>
+        <v>883</v>
       </c>
       <c r="C3" t="n">
-        <v>6190</v>
+        <v>4394</v>
       </c>
       <c r="D3" t="n">
-        <v>23565</v>
+        <v>7582</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3280</v>
+        <v>1263</v>
       </c>
       <c r="C4" t="n">
-        <v>7587</v>
+        <v>4979</v>
       </c>
       <c r="D4" t="n">
-        <v>12673</v>
+        <v>5779</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1725</v>
+        <v>1218</v>
       </c>
       <c r="C5" t="n">
-        <v>3778</v>
+        <v>7350</v>
       </c>
       <c r="D5" t="n">
-        <v>4340</v>
+        <v>2984</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1032</v>
+        <v>625</v>
       </c>
       <c r="C6" t="n">
-        <v>1874</v>
+        <v>7827</v>
       </c>
       <c r="D6" t="n">
-        <v>1171</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>365</v>
+        <v>153</v>
       </c>
       <c r="C7" t="n">
-        <v>1221</v>
+        <v>4908</v>
       </c>
       <c r="D7" t="n">
-        <v>543</v>
+        <v>650</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>125</v>
+        <v>50</v>
       </c>
       <c r="C8" t="n">
-        <v>660</v>
+        <v>1693</v>
       </c>
       <c r="D8" t="n">
-        <v>346</v>
+        <v>469</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="C9" t="n">
-        <v>336</v>
+        <v>465</v>
       </c>
       <c r="D9" t="n">
-        <v>260</v>
+        <v>368</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C10" t="n">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="D10" t="n">
-        <v>212</v>
+        <v>229</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>171</v>
+        <v>151</v>
       </c>
       <c r="D11" t="n">
-        <v>167</v>
+        <v>184</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="D12" t="n">
-        <v>130</v>
+        <v>136</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
         <v>66</v>
       </c>
       <c r="D13" t="n">
-        <v>101</v>
+        <v>94</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="D14" t="n">
-        <v>62</v>
+        <v>55</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>40</v>
+        <v>88</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>33</v>
+        <v>97</v>
       </c>
       <c r="D16" t="n">
-        <v>37</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6876</v>
+        <v>616</v>
       </c>
       <c r="C2" t="n">
-        <v>5513</v>
+        <v>10444</v>
       </c>
       <c r="D2" t="n">
-        <v>22118</v>
+        <v>17134</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4962</v>
+        <v>626</v>
       </c>
       <c r="C3" t="n">
-        <v>3681</v>
+        <v>3496</v>
       </c>
       <c r="D3" t="n">
-        <v>21688</v>
+        <v>7176</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3981</v>
+        <v>978</v>
       </c>
       <c r="C4" t="n">
-        <v>6791</v>
+        <v>4648</v>
       </c>
       <c r="D4" t="n">
-        <v>14169</v>
+        <v>5824</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2121</v>
+        <v>1140</v>
       </c>
       <c r="C5" t="n">
-        <v>5527</v>
+        <v>6150</v>
       </c>
       <c r="D5" t="n">
-        <v>5568</v>
+        <v>3322</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1219</v>
+        <v>781</v>
       </c>
       <c r="C6" t="n">
-        <v>2750</v>
+        <v>7553</v>
       </c>
       <c r="D6" t="n">
-        <v>1642</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>560</v>
+        <v>280</v>
       </c>
       <c r="C7" t="n">
-        <v>1508</v>
+        <v>6155</v>
       </c>
       <c r="D7" t="n">
-        <v>629</v>
+        <v>719</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>186</v>
+        <v>74</v>
       </c>
       <c r="C8" t="n">
-        <v>902</v>
+        <v>2937</v>
       </c>
       <c r="D8" t="n">
-        <v>372</v>
+        <v>487</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>63</v>
+        <v>29</v>
       </c>
       <c r="C9" t="n">
-        <v>469</v>
+        <v>902</v>
       </c>
       <c r="D9" t="n">
-        <v>267</v>
+        <v>379</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C10" t="n">
-        <v>264</v>
+        <v>303</v>
       </c>
       <c r="D10" t="n">
-        <v>217</v>
+        <v>240</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>189</v>
+        <v>175</v>
       </c>
       <c r="D11" t="n">
-        <v>170</v>
+        <v>187</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="D12" t="n">
-        <v>132</v>
+        <v>139</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D13" t="n">
-        <v>102</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="D14" t="n">
-        <v>65</v>
+        <v>57</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>90</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>37</v>
+        <v>97</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4030</v>
+        <v>423</v>
       </c>
       <c r="C2" t="n">
-        <v>2490</v>
+        <v>5598</v>
       </c>
       <c r="D2" t="n">
-        <v>15275</v>
+        <v>12473</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5243</v>
+        <v>885</v>
       </c>
       <c r="C3" t="n">
-        <v>4202</v>
+        <v>5609</v>
       </c>
       <c r="D3" t="n">
-        <v>21215</v>
+        <v>8458</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4398</v>
+        <v>1540</v>
       </c>
       <c r="C4" t="n">
-        <v>6226</v>
+        <v>6677</v>
       </c>
       <c r="D4" t="n">
-        <v>15140</v>
+        <v>5989</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2206</v>
+        <v>784</v>
       </c>
       <c r="C5" t="n">
-        <v>6606</v>
+        <v>9891</v>
       </c>
       <c r="D5" t="n">
-        <v>6050</v>
+        <v>3149</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1024</v>
+        <v>258</v>
       </c>
       <c r="C6" t="n">
-        <v>3416</v>
+        <v>7734</v>
       </c>
       <c r="D6" t="n">
-        <v>1596</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>171</v>
+        <v>68</v>
       </c>
       <c r="C7" t="n">
-        <v>1611</v>
+        <v>2878</v>
       </c>
       <c r="D7" t="n">
-        <v>625</v>
+        <v>575</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>58</v>
+        <v>26</v>
       </c>
       <c r="C8" t="n">
-        <v>751</v>
+        <v>883</v>
       </c>
       <c r="D8" t="n">
-        <v>388</v>
+        <v>371</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="C9" t="n">
-        <v>258</v>
+        <v>296</v>
       </c>
       <c r="D9" t="n">
-        <v>293</v>
+        <v>235</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>185</v>
+        <v>171</v>
       </c>
       <c r="D10" t="n">
-        <v>166</v>
+        <v>183</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="D11" t="n">
-        <v>129</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D12" t="n">
-        <v>99</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>55</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>43</v>
+        <v>88</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>36</v>
+        <v>95</v>
       </c>
       <c r="D15" t="n">
-        <v>35</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4831</v>
+        <v>259</v>
       </c>
       <c r="C2" t="n">
-        <v>2388</v>
+        <v>2586</v>
       </c>
       <c r="D2" t="n">
-        <v>15722</v>
+        <v>8624</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4034</v>
+        <v>588</v>
       </c>
       <c r="C3" t="n">
-        <v>2992</v>
+        <v>4942</v>
       </c>
       <c r="D3" t="n">
-        <v>18981</v>
+        <v>8429</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4147</v>
+        <v>1038</v>
       </c>
       <c r="C4" t="n">
-        <v>5165</v>
+        <v>5823</v>
       </c>
       <c r="D4" t="n">
-        <v>15671</v>
+        <v>5971</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2752</v>
+        <v>770</v>
       </c>
       <c r="C5" t="n">
-        <v>6356</v>
+        <v>7383</v>
       </c>
       <c r="D5" t="n">
-        <v>7262</v>
+        <v>3200</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1353</v>
+        <v>263</v>
       </c>
       <c r="C6" t="n">
-        <v>4795</v>
+        <v>7186</v>
       </c>
       <c r="D6" t="n">
-        <v>2231</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>388</v>
+        <v>58</v>
       </c>
       <c r="C7" t="n">
-        <v>2384</v>
+        <v>3555</v>
       </c>
       <c r="D7" t="n">
-        <v>742</v>
+        <v>541</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>79</v>
+        <v>13</v>
       </c>
       <c r="C8" t="n">
-        <v>1085</v>
+        <v>1047</v>
       </c>
       <c r="D8" t="n">
-        <v>415</v>
+        <v>319</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>429</v>
+        <v>294</v>
       </c>
       <c r="D9" t="n">
-        <v>302</v>
+        <v>186</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>212</v>
+        <v>124</v>
       </c>
       <c r="D10" t="n">
-        <v>177</v>
+        <v>140</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>140</v>
+        <v>74</v>
       </c>
       <c r="D11" t="n">
-        <v>133</v>
+        <v>99</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>84</v>
+        <v>52</v>
       </c>
       <c r="D12" t="n">
-        <v>101</v>
+        <v>63</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>74</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3471</v>
+        <v>279</v>
       </c>
       <c r="C2" t="n">
-        <v>1719</v>
+        <v>8693</v>
       </c>
       <c r="D2" t="n">
-        <v>13093</v>
+        <v>8668</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3762</v>
+        <v>364</v>
       </c>
       <c r="C3" t="n">
-        <v>2487</v>
+        <v>3192</v>
       </c>
       <c r="D3" t="n">
-        <v>17557</v>
+        <v>7934</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3750</v>
+        <v>721</v>
       </c>
       <c r="C4" t="n">
-        <v>4288</v>
+        <v>5267</v>
       </c>
       <c r="D4" t="n">
-        <v>15789</v>
+        <v>6237</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3034</v>
+        <v>810</v>
       </c>
       <c r="C5" t="n">
-        <v>6021</v>
+        <v>6405</v>
       </c>
       <c r="D5" t="n">
-        <v>8149</v>
+        <v>3550</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1606</v>
+        <v>447</v>
       </c>
       <c r="C6" t="n">
-        <v>5490</v>
+        <v>7277</v>
       </c>
       <c r="D6" t="n">
-        <v>2682</v>
+        <v>1643</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>377</v>
+        <v>129</v>
       </c>
       <c r="C7" t="n">
-        <v>3160</v>
+        <v>5367</v>
       </c>
       <c r="D7" t="n">
-        <v>851</v>
+        <v>668</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>64</v>
+        <v>27</v>
       </c>
       <c r="C8" t="n">
-        <v>1409</v>
+        <v>2201</v>
       </c>
       <c r="D8" t="n">
-        <v>439</v>
+        <v>353</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="C9" t="n">
-        <v>515</v>
+        <v>631</v>
       </c>
       <c r="D9" t="n">
-        <v>298</v>
+        <v>202</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>223</v>
+        <v>193</v>
       </c>
       <c r="D10" t="n">
-        <v>181</v>
+        <v>144</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>137</v>
+        <v>94</v>
       </c>
       <c r="D11" t="n">
-        <v>136</v>
+        <v>103</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>82</v>
+        <v>60</v>
       </c>
       <c r="D12" t="n">
-        <v>94</v>
+        <v>66</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>37</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>57</v>
+        <v>10</v>
       </c>
       <c r="D15" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3481,10 +3481,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5525</v>
+        <v>957</v>
       </c>
       <c r="C2" t="n">
-        <v>4947</v>
+        <v>20453</v>
       </c>
       <c r="D2" t="n">
-        <v>15823</v>
+        <v>10874</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3074</v>
+        <v>274</v>
       </c>
       <c r="C3" t="n">
-        <v>1921</v>
+        <v>5156</v>
       </c>
       <c r="D3" t="n">
-        <v>16002</v>
+        <v>7493</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3262</v>
+        <v>489</v>
       </c>
       <c r="C4" t="n">
-        <v>3403</v>
+        <v>4071</v>
       </c>
       <c r="D4" t="n">
-        <v>15412</v>
+        <v>6340</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3024</v>
+        <v>707</v>
       </c>
       <c r="C5" t="n">
-        <v>5163</v>
+        <v>5714</v>
       </c>
       <c r="D5" t="n">
-        <v>9001</v>
+        <v>3880</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1950</v>
+        <v>555</v>
       </c>
       <c r="C6" t="n">
-        <v>5655</v>
+        <v>6792</v>
       </c>
       <c r="D6" t="n">
-        <v>3381</v>
+        <v>1897</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>688</v>
+        <v>233</v>
       </c>
       <c r="C7" t="n">
-        <v>4103</v>
+        <v>6244</v>
       </c>
       <c r="D7" t="n">
-        <v>1075</v>
+        <v>814</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>136</v>
+        <v>59</v>
       </c>
       <c r="C8" t="n">
-        <v>2043</v>
+        <v>3596</v>
       </c>
       <c r="D8" t="n">
-        <v>482</v>
+        <v>395</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="C9" t="n">
-        <v>826</v>
+        <v>1292</v>
       </c>
       <c r="D9" t="n">
-        <v>310</v>
+        <v>218</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>316</v>
+        <v>368</v>
       </c>
       <c r="D10" t="n">
-        <v>192</v>
+        <v>150</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>164</v>
+        <v>131</v>
       </c>
       <c r="D11" t="n">
-        <v>138</v>
+        <v>107</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>97</v>
+        <v>72</v>
       </c>
       <c r="D12" t="n">
-        <v>96</v>
+        <v>69</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="D14" t="n">
-        <v>38</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>59</v>
+        <v>23</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6547</v>
+        <v>4489</v>
       </c>
       <c r="C2" t="n">
-        <v>3485</v>
+        <v>22869</v>
       </c>
       <c r="D2" t="n">
-        <v>14624</v>
+        <v>6772</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>843</v>
+        <v>855</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="C4" t="n">
-        <v>313</v>
+        <v>344</v>
       </c>
       <c r="D4" t="n">
-        <v>1805</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>249</v>
+        <v>314</v>
       </c>
       <c r="C5" t="n">
-        <v>515</v>
+        <v>586</v>
       </c>
       <c r="D5" t="n">
-        <v>1038</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>182</v>
+        <v>255</v>
       </c>
       <c r="C6" t="n">
-        <v>395</v>
+        <v>488</v>
       </c>
       <c r="D6" t="n">
-        <v>777</v>
+        <v>898</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>129</v>
+        <v>202</v>
       </c>
       <c r="C7" t="n">
-        <v>293</v>
+        <v>388</v>
       </c>
       <c r="D7" t="n">
-        <v>496</v>
+        <v>596</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>99</v>
+        <v>171</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>420</v>
+        <v>531</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>75</v>
+        <v>136</v>
       </c>
       <c r="C9" t="n">
-        <v>187</v>
+        <v>277</v>
       </c>
       <c r="D9" t="n">
-        <v>349</v>
+        <v>445</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>53</v>
+        <v>105</v>
       </c>
       <c r="C10" t="n">
-        <v>173</v>
+        <v>265</v>
       </c>
       <c r="D10" t="n">
-        <v>362</v>
+        <v>485</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="C11" t="n">
-        <v>137</v>
+        <v>215</v>
       </c>
       <c r="D11" t="n">
-        <v>245</v>
+        <v>327</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="C12" t="n">
-        <v>104</v>
+        <v>169</v>
       </c>
       <c r="D12" t="n">
-        <v>196</v>
+        <v>274</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="C13" t="n">
-        <v>84</v>
+        <v>142</v>
       </c>
       <c r="D13" t="n">
-        <v>168</v>
+        <v>234</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>128</v>
       </c>
       <c r="D14" t="n">
-        <v>145</v>
+        <v>207</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>127</v>
       </c>
       <c r="D15" t="n">
-        <v>117</v>
+        <v>171</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>124</v>
       </c>
       <c r="D16" t="n">
-        <v>97</v>
+        <v>140</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="C17" t="n">
-        <v>66</v>
+        <v>119</v>
       </c>
       <c r="D17" t="n">
-        <v>76</v>
+        <v>114</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C18" t="n">
-        <v>63</v>
+        <v>116</v>
       </c>
       <c r="D18" t="n">
-        <v>57</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C19" t="n">
-        <v>60</v>
+        <v>111</v>
       </c>
       <c r="D19" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>109</v>
       </c>
       <c r="D20" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21">
@@ -4156,10 +4156,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C21" t="n">
-        <v>72</v>
+        <v>131</v>
       </c>
       <c r="D21" t="n">
         <v>1</v>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3912</v>
+        <v>911</v>
       </c>
       <c r="C2" t="n">
-        <v>2770</v>
+        <v>18134</v>
       </c>
       <c r="D2" t="n">
-        <v>11647</v>
+        <v>9398</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4149</v>
+        <v>440</v>
       </c>
       <c r="C3" t="n">
-        <v>2810</v>
+        <v>10313</v>
       </c>
       <c r="D3" t="n">
-        <v>17262</v>
+        <v>7434</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4461</v>
+        <v>349</v>
       </c>
       <c r="C4" t="n">
-        <v>5024</v>
+        <v>4475</v>
       </c>
       <c r="D4" t="n">
-        <v>15981</v>
+        <v>6324</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1913</v>
+        <v>576</v>
       </c>
       <c r="C5" t="n">
-        <v>7742</v>
+        <v>4830</v>
       </c>
       <c r="D5" t="n">
-        <v>8223</v>
+        <v>4079</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>635</v>
+        <v>568</v>
       </c>
       <c r="C6" t="n">
-        <v>5240</v>
+        <v>6274</v>
       </c>
       <c r="D6" t="n">
-        <v>2562</v>
+        <v>2157</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>125</v>
+        <v>323</v>
       </c>
       <c r="C7" t="n">
-        <v>2002</v>
+        <v>6405</v>
       </c>
       <c r="D7" t="n">
-        <v>619</v>
+        <v>946</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>24</v>
+        <v>108</v>
       </c>
       <c r="C8" t="n">
-        <v>809</v>
+        <v>4658</v>
       </c>
       <c r="D8" t="n">
-        <v>303</v>
+        <v>448</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="C9" t="n">
-        <v>309</v>
+        <v>2172</v>
       </c>
       <c r="D9" t="n">
-        <v>188</v>
+        <v>236</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>160</v>
+        <v>699</v>
       </c>
       <c r="D10" t="n">
-        <v>135</v>
+        <v>157</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>95</v>
+        <v>214</v>
       </c>
       <c r="D11" t="n">
-        <v>94</v>
+        <v>110</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>51</v>
+        <v>90</v>
       </c>
       <c r="D12" t="n">
-        <v>62</v>
+        <v>71</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
+        <v>61</v>
+      </c>
+      <c r="D13" t="n">
         <v>39</v>
-      </c>
-      <c r="D13" t="n">
-        <v>37</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D14" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>69</v>
+        <v>31</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6985</v>
+        <v>5092</v>
       </c>
       <c r="C2" t="n">
-        <v>2533</v>
+        <v>12231</v>
       </c>
       <c r="D2" t="n">
-        <v>29297</v>
+        <v>9496</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2781</v>
+        <v>1448</v>
       </c>
       <c r="C3" t="n">
-        <v>1756</v>
+        <v>9031</v>
       </c>
       <c r="D3" t="n">
-        <v>3096</v>
+        <v>1547</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C4" t="n">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="D4" t="n">
-        <v>1538</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>193</v>
+        <v>148</v>
       </c>
       <c r="C5" t="n">
-        <v>381</v>
+        <v>338</v>
       </c>
       <c r="D5" t="n">
-        <v>1161</v>
+        <v>986</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>200</v>
+        <v>143</v>
       </c>
       <c r="C6" t="n">
-        <v>459</v>
+        <v>356</v>
       </c>
       <c r="D6" t="n">
-        <v>816</v>
+        <v>712</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>102</v>
       </c>
       <c r="C7" t="n">
-        <v>350</v>
+        <v>277</v>
       </c>
       <c r="D7" t="n">
-        <v>538</v>
+        <v>466</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="C8" t="n">
-        <v>260</v>
+        <v>206</v>
       </c>
       <c r="D8" t="n">
-        <v>429</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="C9" t="n">
-        <v>205</v>
+        <v>169</v>
       </c>
       <c r="D9" t="n">
-        <v>354</v>
+        <v>313</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="C10" t="n">
-        <v>180</v>
+        <v>153</v>
       </c>
       <c r="D10" t="n">
-        <v>356</v>
+        <v>324</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>154</v>
+        <v>128</v>
       </c>
       <c r="D11" t="n">
-        <v>261</v>
+        <v>231</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C12" t="n">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>199</v>
+        <v>182</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>154</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>133</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>118</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D18" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>10</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C21" t="n">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4617</v>
+        <v>3497</v>
       </c>
       <c r="C2" t="n">
-        <v>4919</v>
+        <v>6091</v>
       </c>
       <c r="D2" t="n">
-        <v>29445</v>
+        <v>14921</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4010</v>
+        <v>2767</v>
       </c>
       <c r="C3" t="n">
-        <v>1893</v>
+        <v>9383</v>
       </c>
       <c r="D3" t="n">
-        <v>7269</v>
+        <v>2829</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1242</v>
+        <v>695</v>
       </c>
       <c r="C4" t="n">
-        <v>1074</v>
+        <v>5597</v>
       </c>
       <c r="D4" t="n">
-        <v>1805</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="C5" t="n">
-        <v>219</v>
+        <v>209</v>
       </c>
       <c r="D5" t="n">
-        <v>1198</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>185</v>
+        <v>137</v>
       </c>
       <c r="C6" t="n">
-        <v>410</v>
+        <v>341</v>
       </c>
       <c r="D6" t="n">
-        <v>859</v>
+        <v>747</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>114</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>321</v>
       </c>
       <c r="D7" t="n">
-        <v>584</v>
+        <v>509</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>115</v>
+        <v>82</v>
       </c>
       <c r="C8" t="n">
-        <v>307</v>
+        <v>244</v>
       </c>
       <c r="D8" t="n">
-        <v>439</v>
+        <v>395</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85</v>
+        <v>64</v>
       </c>
       <c r="C9" t="n">
-        <v>232</v>
+        <v>188</v>
       </c>
       <c r="D9" t="n">
-        <v>363</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>62</v>
+        <v>48</v>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>161</v>
       </c>
       <c r="D10" t="n">
-        <v>352</v>
+        <v>318</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C11" t="n">
-        <v>164</v>
+        <v>140</v>
       </c>
       <c r="D11" t="n">
-        <v>270</v>
+        <v>244</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C12" t="n">
-        <v>135</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>206</v>
+        <v>187</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>172</v>
+        <v>155</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>9</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C21" t="n">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6099</v>
+        <v>3538</v>
       </c>
       <c r="C2" t="n">
-        <v>3433</v>
+        <v>5076</v>
       </c>
       <c r="D2" t="n">
-        <v>27429</v>
+        <v>18570</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3552</v>
+        <v>2581</v>
       </c>
       <c r="C3" t="n">
-        <v>3066</v>
+        <v>6485</v>
       </c>
       <c r="D3" t="n">
-        <v>10293</v>
+        <v>4652</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2234</v>
+        <v>1504</v>
       </c>
       <c r="C4" t="n">
-        <v>1515</v>
+        <v>7697</v>
       </c>
       <c r="D4" t="n">
-        <v>2799</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>559</v>
+        <v>338</v>
       </c>
       <c r="C5" t="n">
-        <v>682</v>
+        <v>3256</v>
       </c>
       <c r="D5" t="n">
-        <v>1260</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>148</v>
+        <v>112</v>
       </c>
       <c r="C6" t="n">
-        <v>300</v>
+        <v>264</v>
       </c>
       <c r="D6" t="n">
-        <v>908</v>
+        <v>784</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>117</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>331</v>
       </c>
       <c r="D7" t="n">
-        <v>620</v>
+        <v>548</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>125</v>
+        <v>90</v>
       </c>
       <c r="C8" t="n">
-        <v>358</v>
+        <v>283</v>
       </c>
       <c r="D8" t="n">
-        <v>460</v>
+        <v>411</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>90</v>
+        <v>66</v>
       </c>
       <c r="C9" t="n">
-        <v>268</v>
+        <v>215</v>
       </c>
       <c r="D9" t="n">
-        <v>371</v>
+        <v>325</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="C10" t="n">
-        <v>208</v>
+        <v>173</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>314</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="C11" t="n">
-        <v>176</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>280</v>
+        <v>253</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C12" t="n">
-        <v>147</v>
+        <v>124</v>
       </c>
       <c r="D12" t="n">
-        <v>213</v>
+        <v>191</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>116</v>
+        <v>97</v>
       </c>
       <c r="D13" t="n">
-        <v>173</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C15" t="n">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C21" t="n">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6599</v>
+        <v>2445</v>
       </c>
       <c r="C2" t="n">
-        <v>3702</v>
+        <v>4956</v>
       </c>
       <c r="D2" t="n">
-        <v>32280</v>
+        <v>14452</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3897</v>
+        <v>2502</v>
       </c>
       <c r="C3" t="n">
-        <v>2833</v>
+        <v>4970</v>
       </c>
       <c r="D3" t="n">
-        <v>12173</v>
+        <v>6543</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2469</v>
+        <v>1734</v>
       </c>
       <c r="C4" t="n">
-        <v>2302</v>
+        <v>6862</v>
       </c>
       <c r="D4" t="n">
-        <v>4053</v>
+        <v>2186</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1145</v>
+        <v>774</v>
       </c>
       <c r="C5" t="n">
-        <v>1107</v>
+        <v>5575</v>
       </c>
       <c r="D5" t="n">
-        <v>1502</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>305</v>
+        <v>199</v>
       </c>
       <c r="C6" t="n">
-        <v>491</v>
+        <v>1812</v>
       </c>
       <c r="D6" t="n">
-        <v>956</v>
+        <v>818</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>144</v>
+        <v>107</v>
       </c>
       <c r="C7" t="n">
-        <v>350</v>
+        <v>296</v>
       </c>
       <c r="D7" t="n">
-        <v>655</v>
+        <v>584</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>129</v>
+        <v>95</v>
       </c>
       <c r="C8" t="n">
-        <v>382</v>
+        <v>306</v>
       </c>
       <c r="D8" t="n">
-        <v>481</v>
+        <v>429</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>97</v>
+        <v>71</v>
       </c>
       <c r="C9" t="n">
-        <v>310</v>
+        <v>244</v>
       </c>
       <c r="D9" t="n">
-        <v>377</v>
+        <v>331</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="C10" t="n">
-        <v>232</v>
+        <v>192</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>312</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="C11" t="n">
-        <v>190</v>
+        <v>159</v>
       </c>
       <c r="D11" t="n">
-        <v>286</v>
+        <v>259</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>159</v>
+        <v>134</v>
       </c>
       <c r="D12" t="n">
-        <v>217</v>
+        <v>195</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C13" t="n">
-        <v>127</v>
+        <v>107</v>
       </c>
       <c r="D13" t="n">
-        <v>176</v>
+        <v>160</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C16" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C21" t="n">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8015</v>
+        <v>1957</v>
       </c>
       <c r="C2" t="n">
-        <v>3409</v>
+        <v>7438</v>
       </c>
       <c r="D2" t="n">
-        <v>26279</v>
+        <v>12730</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3807</v>
+        <v>2052</v>
       </c>
       <c r="C3" t="n">
-        <v>2689</v>
+        <v>4335</v>
       </c>
       <c r="D3" t="n">
-        <v>13521</v>
+        <v>7231</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1988</v>
+        <v>1786</v>
       </c>
       <c r="C4" t="n">
-        <v>2132</v>
+        <v>5672</v>
       </c>
       <c r="D4" t="n">
-        <v>4688</v>
+        <v>2851</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>944</v>
+        <v>1064</v>
       </c>
       <c r="C5" t="n">
-        <v>1272</v>
+        <v>6113</v>
       </c>
       <c r="D5" t="n">
-        <v>1558</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>346</v>
+        <v>408</v>
       </c>
       <c r="C6" t="n">
-        <v>537</v>
+        <v>3635</v>
       </c>
       <c r="D6" t="n">
-        <v>791</v>
+        <v>854</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>97</v>
+        <v>135</v>
       </c>
       <c r="C7" t="n">
-        <v>269</v>
+        <v>1023</v>
       </c>
       <c r="D7" t="n">
-        <v>518</v>
+        <v>617</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>58</v>
+        <v>92</v>
       </c>
       <c r="C8" t="n">
-        <v>221</v>
+        <v>298</v>
       </c>
       <c r="D8" t="n">
-        <v>361</v>
+        <v>448</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>75</v>
       </c>
       <c r="C9" t="n">
-        <v>201</v>
+        <v>271</v>
       </c>
       <c r="D9" t="n">
-        <v>269</v>
+        <v>338</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>30</v>
+        <v>54</v>
       </c>
       <c r="C10" t="n">
-        <v>151</v>
+        <v>214</v>
       </c>
       <c r="D10" t="n">
-        <v>237</v>
+        <v>311</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="C11" t="n">
-        <v>114</v>
+        <v>172</v>
       </c>
       <c r="D11" t="n">
-        <v>194</v>
+        <v>261</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>93</v>
+        <v>143</v>
       </c>
       <c r="D12" t="n">
-        <v>148</v>
+        <v>201</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C13" t="n">
-        <v>73</v>
+        <v>115</v>
       </c>
       <c r="D13" t="n">
-        <v>116</v>
+        <v>162</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>92</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>76</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C16" t="n">
-        <v>38</v>
+        <v>67</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>93</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>75</v>
+        <v>131</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7004</v>
+        <v>3149</v>
       </c>
       <c r="C2" t="n">
-        <v>7144</v>
+        <v>12933</v>
       </c>
       <c r="D2" t="n">
-        <v>26996</v>
+        <v>17537</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4986</v>
+        <v>1671</v>
       </c>
       <c r="C3" t="n">
-        <v>2674</v>
+        <v>5073</v>
       </c>
       <c r="D3" t="n">
-        <v>14749</v>
+        <v>7492</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2532</v>
+        <v>1632</v>
       </c>
       <c r="C4" t="n">
-        <v>2429</v>
+        <v>4899</v>
       </c>
       <c r="D4" t="n">
-        <v>6411</v>
+        <v>3451</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1316</v>
+        <v>1223</v>
       </c>
       <c r="C5" t="n">
-        <v>1757</v>
+        <v>5778</v>
       </c>
       <c r="D5" t="n">
-        <v>2141</v>
+        <v>1514</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>599</v>
+        <v>617</v>
       </c>
       <c r="C6" t="n">
-        <v>948</v>
+        <v>4681</v>
       </c>
       <c r="D6" t="n">
-        <v>919</v>
+        <v>902</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>204</v>
+        <v>221</v>
       </c>
       <c r="C7" t="n">
-        <v>423</v>
+        <v>2200</v>
       </c>
       <c r="D7" t="n">
-        <v>566</v>
+        <v>647</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>71</v>
+        <v>101</v>
       </c>
       <c r="C8" t="n">
-        <v>247</v>
+        <v>607</v>
       </c>
       <c r="D8" t="n">
-        <v>386</v>
+        <v>468</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="C9" t="n">
-        <v>211</v>
+        <v>282</v>
       </c>
       <c r="D9" t="n">
-        <v>279</v>
+        <v>346</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>33</v>
+        <v>57</v>
       </c>
       <c r="C10" t="n">
-        <v>176</v>
+        <v>236</v>
       </c>
       <c r="D10" t="n">
-        <v>240</v>
+        <v>311</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="C11" t="n">
-        <v>132</v>
+        <v>186</v>
       </c>
       <c r="D11" t="n">
-        <v>199</v>
+        <v>262</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="C12" t="n">
-        <v>103</v>
+        <v>153</v>
       </c>
       <c r="D12" t="n">
-        <v>152</v>
+        <v>206</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>82</v>
+        <v>124</v>
       </c>
       <c r="D13" t="n">
-        <v>119</v>
+        <v>163</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>64</v>
+        <v>98</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>137</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>81</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>69</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>93</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>84</v>
+        <v>143</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6002</v>
+        <v>2818</v>
       </c>
       <c r="C2" t="n">
-        <v>5683</v>
+        <v>8277</v>
       </c>
       <c r="D2" t="n">
-        <v>31866</v>
+        <v>13964</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4925</v>
+        <v>2515</v>
       </c>
       <c r="C3" t="n">
-        <v>4455</v>
+        <v>8679</v>
       </c>
       <c r="D3" t="n">
-        <v>15646</v>
+        <v>8251</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3224</v>
+        <v>1130</v>
       </c>
       <c r="C4" t="n">
-        <v>2519</v>
+        <v>8509</v>
       </c>
       <c r="D4" t="n">
-        <v>7755</v>
+        <v>3336</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1701</v>
+        <v>570</v>
       </c>
       <c r="C5" t="n">
-        <v>2077</v>
+        <v>4587</v>
       </c>
       <c r="D5" t="n">
-        <v>2895</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>870</v>
+        <v>204</v>
       </c>
       <c r="C6" t="n">
-        <v>1379</v>
+        <v>2156</v>
       </c>
       <c r="D6" t="n">
-        <v>1120</v>
+        <v>634</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>360</v>
+        <v>93</v>
       </c>
       <c r="C7" t="n">
-        <v>705</v>
+        <v>594</v>
       </c>
       <c r="D7" t="n">
-        <v>625</v>
+        <v>458</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>120</v>
+        <v>69</v>
       </c>
       <c r="C8" t="n">
-        <v>338</v>
+        <v>276</v>
       </c>
       <c r="D8" t="n">
-        <v>413</v>
+        <v>339</v>
       </c>
     </row>
     <row r="9">
@@ -6479,10 +6479,10 @@
         <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="D9" t="n">
-        <v>291</v>
+        <v>304</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C10" t="n">
-        <v>193</v>
+        <v>182</v>
       </c>
       <c r="D10" t="n">
-        <v>244</v>
+        <v>256</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="D12" t="n">
-        <v>155</v>
+        <v>159</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="D13" t="n">
-        <v>122</v>
+        <v>134</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C14" t="n">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>111</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C15" t="n">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>73</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
     </row>
     <row r="18">
@@ -6602,10 +6602,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>143</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>92</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
